--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>46198</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>46122</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44788</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>45457</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45863</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>46135</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>44515</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>44991</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>44532</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45511</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>46266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>44559</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>45701</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>44463</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45505</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>45217</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>45614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>44917</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>46189</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>45457</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>46189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44690</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>45811</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>45250</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44917</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>46100</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>46226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45842</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>45617</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45666</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45155</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44924</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>46083</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>45148</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>46212</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>45254</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45254</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>45793</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45835</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44493</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>44742</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>45230</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45170</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45933</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45944</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45436</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45385</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>46164</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45630</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>46070</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>46181</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>46077</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>45159</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45737</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>46191</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>46198</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>46114</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>46246</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>46248</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45516</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44949</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45159</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>46280</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>45793</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45832</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45867</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45875</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44351</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44635</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>44943</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44845</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44693</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44652</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44876</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44488</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44559</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44600</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44546</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>44714</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44879</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44797</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44875</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44459</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44500</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44463</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44802</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44715</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44872</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44536</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12531,7 +12531,7 @@
         <v>44872</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>44473</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44614</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44537</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>44817</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44679</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>44865</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44685</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44797</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44581</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44839</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44536</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44711</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44860</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44872</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>44743</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44540</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>44511</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44820</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44600</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44713</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>44721</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44488</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44684</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44803</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>44854</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45644</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45551</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45728</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45208</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44851</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45517</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45520</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45057</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45463</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>45775</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>44915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44490</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45453</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45212</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45455</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45238</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>45159</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>44883</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45510</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45299</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45390</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45019</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16271,7 +16271,7 @@
         <v>45104</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44777</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>44889</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45583</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>45309</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44902</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45533</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>44942</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45616</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44935</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>44935</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44935</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>44971</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44910</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>44916</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45729</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45163</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45527</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45511</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45602</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45240</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>45721</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45069</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45518</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44962</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44882</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45148</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45740</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44902</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>45159</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44840</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45646</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>44673</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45250</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45019</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45684</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45155</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45063</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45103</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45104</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>45251</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45723</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>44987</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45642</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45105</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45576</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20069,7 +20069,7 @@
         <v>44559</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>45226</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>44685</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45279</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         <v>45434</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45299</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>45623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>45609</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>45520</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45520</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45525</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45513</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45714</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45686</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45148</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45685</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45114</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45460</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45043</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45219</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>44749</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45463</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45513</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45887</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21871,7 +21871,7 @@
         <v>44794</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45061</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45162</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45560</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45560</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>45559</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45545</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45506</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45706</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>44644</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>46139</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>45863</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45510</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45803</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45894</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45565</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>46136</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>45316</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>45175</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>45387</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>45896</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46136</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45896</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45896</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45897</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45537</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45838</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45898</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45511</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>44825</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45905</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45884</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45842</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45909</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>45789</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45514</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45728</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45534</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45453</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45911</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44749</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45539</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45579</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45915</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>45915</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45915</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45912</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45915</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45915</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45674</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45915</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25958,7 +25958,7 @@
         <v>45616</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>46140</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45915</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45912</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45912</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45912</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45644</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>44974</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45523</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45755</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45580</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45916</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44839</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45916</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>45919</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>45918</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45919</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45511</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45553</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45560</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>45924</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45114</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27770,7 +27770,7 @@
         <v>45924</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>44924</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45145</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45929</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45928</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45928</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>45684</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45320</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>44963</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45643</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>45247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45936</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         <v>45938</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45114</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45005</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45939</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45114</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45945</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45155</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45944</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45944</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45685</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45946</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45737</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>45427</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45946</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45763</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>45947</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45950</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45575</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45737</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45462</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45952</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45452</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45946</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>44491</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45526</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>46153</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45576</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>45397</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>45959</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45959</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45019</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>45961</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45961</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45961</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45961</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45961</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>45961</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>44552</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>45961</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45961</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>45960</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31938,7 +31938,7 @@
         <v>45961</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32011,7 +32011,7 @@
         <v>46155</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32084,7 +32084,7 @@
         <v>45964</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45739</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32230,7 +32230,7 @@
         <v>45964</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>46077</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>45887</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32454,7 +32454,7 @@
         <v>45554</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>45554</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>44917</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45163</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45635</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45971</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>45973</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32970,7 +32970,7 @@
         <v>45973</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45163</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>45616</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33199,7 +33199,7 @@
         <v>44494</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33272,7 +33272,7 @@
         <v>45979</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>45978</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>45979</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45979</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>45645</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33652,7 +33652,7 @@
         <v>45978</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45979</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45622</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45980</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>46155</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34110,7 +34110,7 @@
         <v>45980</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34188,7 +34188,7 @@
         <v>45980</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45980</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45982</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>44659</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45985</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45985</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45159</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44944</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34792,7 +34792,7 @@
         <v>44886</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34865,7 +34865,7 @@
         <v>45537</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45537</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45832</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>44944</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44610</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>46160</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>45988</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45331</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>45993</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45216</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35625,7 +35625,7 @@
         <v>45230</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>45993</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>46161</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44914</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>45841</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36005,7 +36005,7 @@
         <v>45559</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>46160</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45250</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45748</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45993</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>46162</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45512</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45995</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45994</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45260</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>46163</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45338</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>45999</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>46000</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45526</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>45001</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45616</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37281,7 +37281,7 @@
         <v>45616</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45630</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>46000</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45326</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>46001</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>46002</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>46001</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46002</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>46006</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>44925</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>46006</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38109,7 +38109,7 @@
         <v>46167</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>46006</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>46008</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>46009</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>46009</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>46009</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38552,7 +38552,7 @@
         <v>45771</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38630,7 +38630,7 @@
         <v>46009</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45007</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38776,7 +38776,7 @@
         <v>45596</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45540</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38932,7 +38932,7 @@
         <v>46169</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44925</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>44925</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45225</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45135</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39312,7 +39312,7 @@
         <v>45390</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         <v>45597</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45919</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>46031</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>46031</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>46035</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>46171</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39911,7 +39911,7 @@
         <v>45453</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45646</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>46041</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>46174</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>45244</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40286,7 +40286,7 @@
         <v>44910</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>44973</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>46171</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45625</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>46171</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40671,7 +40671,7 @@
         <v>46175</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>46049</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40817,7 +40817,7 @@
         <v>45405</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>46175</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45425</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45554</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>46177</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>46059</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>46177</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45328</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>46059</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45474</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>45468</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41655,7 +41655,7 @@
         <v>46065</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>44886</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>46066</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41879,7 +41879,7 @@
         <v>46181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>46181</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42030,7 +42030,7 @@
         <v>46070</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>46181</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42186,7 +42186,7 @@
         <v>44924</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>45513</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42342,7 +42342,7 @@
         <v>45385</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>46073</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>46072</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42566,7 +42566,7 @@
         <v>46073</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42639,7 +42639,7 @@
         <v>46073</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>46077</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45509</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42858,7 +42858,7 @@
         <v>46076</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>46078</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43009,7 +43009,7 @@
         <v>44845</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45229</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43155,7 +43155,7 @@
         <v>46079</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43228,7 +43228,7 @@
         <v>45559</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>44889</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45104</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43462,7 +43462,7 @@
         <v>46084</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>46084</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>44818</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46184</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>46084</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>44902</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>46083</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>46188</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>46085</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45596</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44197,7 +44197,7 @@
         <v>45420</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>44641</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45616</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         <v>45719</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>45569</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         <v>46185</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45232</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45763</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>46185</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>46185</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>45538</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45113,7 +45113,7 @@
         <v>45537</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>46189</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46091</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>44911</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>46091</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>44693</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>46189</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45639,7 +45639,7 @@
         <v>45754</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>45226</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45453</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>46097</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45946,7 +45946,7 @@
         <v>46099</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>46099</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46092,7 +46092,7 @@
         <v>45583</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46170,7 +46170,7 @@
         <v>46195</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45645</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>46195</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>46100</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>46195</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>46196</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46623,7 +46623,7 @@
         <v>46196</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>46196</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>46196</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>46196</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>46101</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45569</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>46195</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>46196</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>46198</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>46198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>46198</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>46198</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>46198</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>45560</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>45596</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45596</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45677</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>46107</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>45532</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>46107</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48123,7 +48123,7 @@
         <v>46198</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>46111</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45748</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>46199</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46112</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>46113</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48659,7 +48659,7 @@
         <v>46113</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>46113</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>46113</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45344</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45145</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>46120</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>45327</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>46120</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>44881</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>46199</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>46122</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>45267</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>46202</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49706,7 +49706,7 @@
         <v>46245</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>46244</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>46244</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45737</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>46184</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>46128</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50169,7 +50169,7 @@
         <v>46203</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>46245</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45537</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45211</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>46134</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>45151</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45541</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>45541</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45069</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45559</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45453</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>46134</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51085,7 +51085,7 @@
         <v>45187</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45113</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51231,7 +51231,7 @@
         <v>44971</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>45329</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         <v>45684</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>45161</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51528,7 +51528,7 @@
         <v>44916</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>46246</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>46204</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>44925</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>44614</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         <v>44479</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45513</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>44860</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52132,7 +52132,7 @@
         <v>46204</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45740</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45560</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45560</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45254</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45734</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>46206</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45665</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>46248</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45715</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>46251</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>46205</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>46251</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>46251</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53199,7 +53199,7 @@
         <v>45740</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>44925</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>44925</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>46251</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>46248</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45518</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>46205</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>46252</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>45068</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>45559</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53949,7 +53949,7 @@
         <v>46252</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>45530</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>46247</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>45484</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54251,7 +54251,7 @@
         <v>46252</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>46252</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>46254</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>44565</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>46254</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54616,7 +54616,7 @@
         <v>44572</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54689,7 +54689,7 @@
         <v>44925</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54762,7 +54762,7 @@
         <v>45460</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54840,7 +54840,7 @@
         <v>46213</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>45568</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54991,7 +54991,7 @@
         <v>45105</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55069,7 +55069,7 @@
         <v>46213</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45306</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45520</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55303,7 +55303,7 @@
         <v>45261</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55381,7 +55381,7 @@
         <v>46219</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>45338</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>46265</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55605,7 +55605,7 @@
         <v>45635</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55678,7 +55678,7 @@
         <v>46262</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55751,7 +55751,7 @@
         <v>46220</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>46265</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>46220</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55980,7 +55980,7 @@
         <v>46220</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>45589</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45589</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>46219</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>45832</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56370,7 +56370,7 @@
         <v>46265</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56443,7 +56443,7 @@
         <v>46219</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56521,7 +56521,7 @@
         <v>46219</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56599,7 +56599,7 @@
         <v>46219</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56677,7 +56677,7 @@
         <v>46266</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56755,7 +56755,7 @@
         <v>45628</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56833,7 +56833,7 @@
         <v>46251</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56911,7 +56911,7 @@
         <v>45628</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         <v>46267</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>46265</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57140,7 +57140,7 @@
         <v>45453</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>45453</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>46267</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57369,7 +57369,7 @@
         <v>45754</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>46267</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46266</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>45614</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45666</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         <v>45210</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>45701</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>46241</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>46268</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45600</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45643</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58202,7 +58202,7 @@
         <v>45646</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>45630</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45737</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58426,7 +58426,7 @@
         <v>46269</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>45776</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58577,7 +58577,7 @@
         <v>45777</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>46269</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58733,7 +58733,7 @@
         <v>46269</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         <v>46269</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45777</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58967,7 +58967,7 @@
         <v>45776</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59040,7 +59040,7 @@
         <v>44875</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45782</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>45783</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45559</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59352,7 +59352,7 @@
         <v>46230</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>46230</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>46275</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>46275</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>46275</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>46275</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>46234</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>46234</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>46234</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60054,7 +60054,7 @@
         <v>46234</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60132,7 +60132,7 @@
         <v>45785</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>46119</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60283,7 +60283,7 @@
         <v>46280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60356,7 +60356,7 @@
         <v>46237</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60434,7 +60434,7 @@
         <v>46280</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45296</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45460</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60658,7 +60658,7 @@
         <v>46238</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60731,7 +60731,7 @@
         <v>46281</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60809,7 +60809,7 @@
         <v>46282</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60882,7 +60882,7 @@
         <v>45793</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>44652</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61028,7 +61028,7 @@
         <v>45796</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61106,7 +61106,7 @@
         <v>45671</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61179,7 +61179,7 @@
         <v>46282</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>46241</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45320</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>46282</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45794</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61554,7 +61554,7 @@
         <v>46241</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61632,7 +61632,7 @@
         <v>46240</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61710,7 +61710,7 @@
         <v>46241</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>46282</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>46241</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45567</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>46282</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45805</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>44868</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45807</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62314,7 +62314,7 @@
         <v>45807</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>45811</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62470,7 +62470,7 @@
         <v>45181</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62543,7 +62543,7 @@
         <v>45810</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62621,7 +62621,7 @@
         <v>45330</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62694,7 +62694,7 @@
         <v>45811</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62772,7 +62772,7 @@
         <v>45603</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62845,7 +62845,7 @@
         <v>45483</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>45816</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63001,7 +63001,7 @@
         <v>45817</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>45817</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63152,7 +63152,7 @@
         <v>45819</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63225,7 +63225,7 @@
         <v>45820</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63303,7 +63303,7 @@
         <v>45825</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63376,7 +63376,7 @@
         <v>45825</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45825</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63522,7 +63522,7 @@
         <v>45827</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63600,7 +63600,7 @@
         <v>45831</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63678,7 +63678,7 @@
         <v>45831</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63756,7 +63756,7 @@
         <v>45829</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63829,7 +63829,7 @@
         <v>45831</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45832</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63985,7 +63985,7 @@
         <v>45832</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45835</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>45835</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64219,7 +64219,7 @@
         <v>45835</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64297,7 +64297,7 @@
         <v>45834</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45835</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64448,7 +64448,7 @@
         <v>45838</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64521,7 +64521,7 @@
         <v>45841</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>45847</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64677,7 +64677,7 @@
         <v>45861</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64755,7 +64755,7 @@
         <v>45861</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64833,7 +64833,7 @@
         <v>45867</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45867</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64989,7 +64989,7 @@
         <v>45868</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65062,7 +65062,7 @@
         <v>45875</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65140,7 +65140,7 @@
         <v>45875</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65218,7 +65218,7 @@
         <v>45875</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         <v>45882</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65374,7 +65374,7 @@
         <v>45882</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65452,7 +65452,7 @@
         <v>45882</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65530,7 +65530,7 @@
         <v>44463</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65603,7 +65603,7 @@
         <v>44635</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65676,7 +65676,7 @@
         <v>45673</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65754,7 +65754,7 @@
         <v>45392</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65827,7 +65827,7 @@
         <v>44607</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65905,7 +65905,7 @@
         <v>44603</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65983,7 +65983,7 @@
         <v>44713</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66056,7 +66056,7 @@
         <v>45249</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66134,7 +66134,7 @@
         <v>44904</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66212,7 +66212,7 @@
         <v>44635</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66285,7 +66285,7 @@
         <v>45747</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66363,7 +66363,7 @@
         <v>45747</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66441,7 +66441,7 @@
         <v>45747</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66519,7 +66519,7 @@
         <v>45747</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66597,7 +66597,7 @@
         <v>45747</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66675,7 +66675,7 @@
         <v>45776</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66753,7 +66753,7 @@
         <v>45775</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66826,7 +66826,7 @@
         <v>45916</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66899,7 +66899,7 @@
         <v>46114</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>46149</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46122</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>44788</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45863</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46198</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45457</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45217</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44690</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>45811</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45457</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46100</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44917</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45793</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>46083</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45155</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45666</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45617</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>46212</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44924</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45148</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45254</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45793</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>46077</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45737</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45385</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45230</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45944</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>46114</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45867</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>46181</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>46191</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45875</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>46198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>46203</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>46280</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45436</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45159</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>46248</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>46246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45630</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44949</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44943</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44693</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44652</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44559</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44714</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44802</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44715</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44872</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44473</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44614</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44797</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>44581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>44839</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44711</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>44860</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44872</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44820</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44600</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>44713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44721</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44488</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44854</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45734</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44839</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45512</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44794</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>44825</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45754</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44818</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45723</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45719</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45338</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45208</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45225</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45453</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45455</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45299</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45420</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45453</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45114</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45576</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44845</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45453</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45390</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45397</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44962</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44652</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45306</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45671</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45509</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45919</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44889</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45247</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45453</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45267</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45793</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45320</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45794</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45545</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44882</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45796</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44881</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>44883</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45506</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>46031</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46031</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>46035</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45510</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45803</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>46041</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45894</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45329</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45896</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45898</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45537</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45538</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45897</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45425</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>46049</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45737</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45905</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45909</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45912</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45513</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44924</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45915</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45616</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45616</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45616</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45915</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45916</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46059</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44942</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45474</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45525</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45523</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>46059</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>44552</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45919</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45567</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46065</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45007</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45919</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46066</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46070</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45924</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45240</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45924</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>46072</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>46073</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45513</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46076</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>46073</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45232</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46077</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>46079</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45929</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45805</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45928</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>44614</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45517</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44868</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45721</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45807</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45181</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45554</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45807</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46084</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>46085</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46084</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44971</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45330</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45810</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45938</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45385</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45212</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46091</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45583</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45939</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44610</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>46097</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>46099</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45944</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46099</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45945</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45946</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46101</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>46100</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45811</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45946</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45569</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45526</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45947</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44641</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45950</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45684</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45226</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45952</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45952</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44944</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46107</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46107</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45946</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46111</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46112</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>46113</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45260</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46113</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46113</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>46113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45959</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45603</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45959</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>46120</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45960</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45961</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45961</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45961</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45961</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45961</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46120</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45964</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46122</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45961</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45961</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45019</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45537</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45811</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45299</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44924</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45817</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45973</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45219</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45978</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46128</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45979</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>44925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>45980</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45979</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44971</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45979</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45019</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45979</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46134</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45980</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>46134</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45982</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45985</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45068</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46136</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>45842</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45993</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45993</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45994</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45674</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45995</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45005</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46000</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45114</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45114</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45103</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45104</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45817</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46001</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45162</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46001</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44565</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46002</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45483</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>46006</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>46006</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45789</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45714</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45646</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45685</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45838</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45819</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45820</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46009</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45665</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45646</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46009</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46009</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>46139</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45706</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>46140</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45513</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45737</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45739</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45884</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45554</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45863</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>44749</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45514</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45161</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44886</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45526</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45825</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45061</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45825</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45737</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45453</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45250</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45043</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45511</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45827</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45539</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45755</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45616</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45534</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45832</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45069</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45832</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44851</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45829</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45771</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45831</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45831</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44644</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45834</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>44925</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>46153</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45597</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45635</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>46155</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45887</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45740</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>46077</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>44490</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>46160</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45835</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45835</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45835</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44910</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46160</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45560</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45596</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45838</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45835</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45559</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45460</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45559</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45559</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46161</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45576</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45832</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45113</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45320</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45644</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45841</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>46163</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>46162</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45344</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>46167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45551</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45105</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>46169</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>46171</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45580</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44491</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45861</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45537</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45537</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45861</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>46171</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44935</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44935</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44935</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45602</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46171</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46174</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>46175</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45868</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>44494</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45867</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45867</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>45510</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>46177</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44973</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45575</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>46181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>46181</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45616</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45527</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45754</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44916</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>45019</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45569</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>46185</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45148</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>46184</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45145</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>45114</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>46189</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45518</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45518</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45533</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>46189</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>46188</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45635</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45155</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45159</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>44911</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45875</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>46195</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45875</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>46195</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45875</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>46195</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>46196</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>46196</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45554</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46196</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45513</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>46196</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45614</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46196</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>46196</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45568</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45559</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>46198</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>46198</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45596</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45628</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>46198</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>46198</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>46198</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>46198</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>46199</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45452</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>46198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45609</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45579</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>45737</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45216</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45882</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45645</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45882</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45882</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>46184</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45589</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>46205</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45427</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46204</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46205</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45063</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>46204</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46252</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>46252</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45629</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>46251</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>46252</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>46252</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45715</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>46251</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45623</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45167</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46254</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46254</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45728</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>44673</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45434</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46213</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45159</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>45645</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>45583</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45642</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45763</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45740</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>44777</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>44693</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45226</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>46219</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>46219</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46219</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>46219</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45463</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45211</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44910</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45643</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45135</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>46266</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>46220</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>46265</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45316</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46220</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>46262</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46220</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46251</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46265</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45238</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>46265</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45230</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45832</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46265</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46266</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>45327</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>44974</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45309</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>46267</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         <v>45163</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>46268</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>46267</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>46267</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53260,7 +53260,7 @@
         <v>45254</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45250</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>44749</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53479,7 +53479,7 @@
         <v>46269</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>46269</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>46269</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>46269</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>46241</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45462</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>46230</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>44925</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54093,7 +54093,7 @@
         <v>45229</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45559</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54244,7 +54244,7 @@
         <v>46230</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>46275</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>46275</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>46275</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45484</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>46275</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45748</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54785,7 +54785,7 @@
         <v>46280</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>44685</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>46280</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>46237</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>46234</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>46119</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45163</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>46234</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>46234</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45148</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>46238</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45740</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>46281</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>46282</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>46282</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>46282</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>46282</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45589</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>46285</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>46285</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>46241</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46285</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45326</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>46185</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>46286</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>46240</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>45405</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56879,7 +56879,7 @@
         <v>45520</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45560</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57035,7 +57035,7 @@
         <v>45560</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>44915</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>46241</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>44925</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>44925</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>45331</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>46285</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>46285</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>46241</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>46287</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>46288</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>46244</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>44917</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45816</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45560</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45560</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>46245</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46248</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>46219</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45540</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>45596</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58784,7 +58784,7 @@
         <v>45596</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>45622</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45463</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45251</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46199</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>46248</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>45001</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>46246</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>44889</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45104</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>46247</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45520</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59695,7 +59695,7 @@
         <v>44659</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45338</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>44902</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45174</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45520</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>45387</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45151</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>45210</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>45565</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45175</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45057</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>45600</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>45684</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>45148</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45684</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60825,7 +60825,7 @@
         <v>44840</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45453</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60971,7 +60971,7 @@
         <v>45646</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61044,7 +61044,7 @@
         <v>45775</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>44902</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>45559</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>45520</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>44860</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45460</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44559</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45677</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45105</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45625</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45628</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61872,7 +61872,7 @@
         <v>45616</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45145</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>44925</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>44925</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>44479</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         <v>45261</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>45328</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62403,7 +62403,7 @@
         <v>45215</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45560</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>45686</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>45069</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45666</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62778,7 +62778,7 @@
         <v>45763</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62856,7 +62856,7 @@
         <v>44963</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62929,7 +62929,7 @@
         <v>45748</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>44987</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45511</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         <v>45729</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45159</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45453</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45530</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63450,7 +63450,7 @@
         <v>45541</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45541</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45685</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63679,7 +63679,7 @@
         <v>45644</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63752,7 +63752,7 @@
         <v>45630</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>44944</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45701</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>44572</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>45776</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45776</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45777</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64278,7 +64278,7 @@
         <v>45777</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>44875</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45782</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>45783</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45785</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45460</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>45296</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>44463</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>44635</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>44607</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65038,7 +65038,7 @@
         <v>44603</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65116,7 +65116,7 @@
         <v>44713</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>44635</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>45673</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45392</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65413,7 +65413,7 @@
         <v>45249</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>44904</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65569,7 +65569,7 @@
         <v>45747</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65647,7 +65647,7 @@
         <v>45747</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65725,7 +65725,7 @@
         <v>45747</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65803,7 +65803,7 @@
         <v>45747</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         <v>45747</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>45776</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66037,7 +66037,7 @@
         <v>45775</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66110,7 +66110,7 @@
         <v>45916</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66183,7 +66183,7 @@
         <v>46114</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         <v>46149</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46122</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>44788</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45863</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46198</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45457</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>46176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>45505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45217</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44690</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>45811</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45457</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46100</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44917</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45793</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>46083</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>45155</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>45666</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45617</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>46212</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44924</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45148</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45254</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45793</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>46077</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>45737</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45385</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45933</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45230</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45944</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>46114</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45159</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45867</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>46181</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>46191</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>45875</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>46198</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>46203</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>45170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44742</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>46280</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45436</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45159</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>46248</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>46246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45630</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44949</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44943</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44693</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44652</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44559</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44714</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44802</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44715</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44872</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44473</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44614</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44797</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>44581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>44839</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44536</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44711</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>44860</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44872</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44743</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44820</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44600</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>44713</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44721</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44488</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44854</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>45728</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45734</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45553</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44839</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45512</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44794</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>44825</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45754</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>44818</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>45723</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45719</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45338</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45208</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45225</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45453</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45455</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45299</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45420</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45453</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45114</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45576</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44845</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45453</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45390</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45397</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44962</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44652</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45306</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45671</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45509</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45919</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>44889</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45247</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>45453</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>45267</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45793</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>45320</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45794</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>45545</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44882</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45796</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45511</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44881</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>44883</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45506</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>46031</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>46031</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>46031</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45887</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>46035</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45510</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45803</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>46041</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         <v>45894</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45329</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>45896</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>45896</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45898</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45537</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45538</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>45897</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45425</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>46049</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45737</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45905</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45909</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45912</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45912</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45912</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45513</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44924</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45915</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45916</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45616</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45616</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45616</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45915</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45915</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>45916</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46059</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44942</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45474</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45525</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45523</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>46059</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45918</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>44552</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45919</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45567</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>46065</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45007</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45919</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22589,7 +22589,7 @@
         <v>46066</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>46070</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45924</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45240</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45924</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>46072</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>46073</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45513</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46076</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>46073</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45232</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>46077</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>46079</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45929</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45805</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45928</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>44614</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>46083</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45517</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24235,7 +24235,7 @@
         <v>44868</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24308,7 +24308,7 @@
         <v>45721</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24381,7 +24381,7 @@
         <v>45807</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>45181</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24532,7 +24532,7 @@
         <v>45554</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45807</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>46084</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>46085</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46084</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44971</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45330</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>45936</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45810</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45938</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45385</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45212</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>46091</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>46091</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45583</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44916</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45939</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44610</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>46097</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>46099</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45944</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45944</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>46099</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45945</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45946</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46101</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>46100</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45811</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45946</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45569</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45526</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45947</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44641</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45950</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45684</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45226</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45952</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45952</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44944</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46107</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46107</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45946</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46111</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46112</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>46113</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45260</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>46113</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>46113</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>46113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>45959</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45603</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>45959</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>46120</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45960</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45961</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>45961</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29022,7 +29022,7 @@
         <v>45964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45961</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45961</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45961</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>46120</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45964</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>46122</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45961</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29689,7 +29689,7 @@
         <v>45961</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>45019</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45537</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45811</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45299</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>44924</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45817</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45973</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45219</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30507,7 +30507,7 @@
         <v>45643</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45978</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46128</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>45979</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>44925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>45980</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45979</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44971</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31194,7 +31194,7 @@
         <v>45979</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45980</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45019</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45980</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45979</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>46134</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45980</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>46134</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45982</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45985</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45985</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45988</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45155</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>45068</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>46136</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>45842</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45993</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45993</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45994</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45674</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45995</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45005</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>46000</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>45114</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>45114</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45999</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45103</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45104</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45817</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33600,7 +33600,7 @@
         <v>46001</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45162</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>46001</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>46002</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33897,7 +33897,7 @@
         <v>44565</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>46002</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45483</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>46006</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34194,7 +34194,7 @@
         <v>46006</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34272,7 +34272,7 @@
         <v>45789</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45714</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45187</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45646</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>46008</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45685</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45838</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45819</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45820</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         <v>46009</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45665</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45646</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46009</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46009</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>46139</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45706</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>46140</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45513</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45737</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45739</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45884</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45554</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45863</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>44749</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>45514</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45161</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>44886</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45526</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45825</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>45061</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>45825</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45737</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>45453</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45250</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45043</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45511</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45827</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45539</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45755</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45616</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45831</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45534</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37632,7 +37632,7 @@
         <v>45832</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45069</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>45832</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>44851</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45829</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45771</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45831</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45831</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44644</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>45834</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>44925</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>46153</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45597</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45635</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>46155</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>46155</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45887</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45740</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>46077</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>44490</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>46160</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45835</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45835</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45835</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44910</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>46160</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45560</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45596</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45838</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45835</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45559</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>45460</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45559</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45559</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>46161</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45576</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45832</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45113</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>45320</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45644</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45841</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40813,7 +40813,7 @@
         <v>46163</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>46162</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45344</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>46167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45551</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41266,7 +41266,7 @@
         <v>45105</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>46169</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>46171</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>45580</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>44491</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45861</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45537</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45537</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45861</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>46171</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44935</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42109,7 +42109,7 @@
         <v>44935</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44935</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42265,7 +42265,7 @@
         <v>45602</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42338,7 +42338,7 @@
         <v>46171</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46174</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>46175</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45868</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>44494</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45867</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>46177</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42869,7 +42869,7 @@
         <v>45867</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42947,7 +42947,7 @@
         <v>45510</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>46177</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>44973</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45575</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>46181</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>46181</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45616</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45527</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45754</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44916</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         <v>45019</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45569</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>46185</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>45148</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>46184</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>46185</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45145</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>45114</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>46189</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44462,7 +44462,7 @@
         <v>45518</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45518</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44608,7 +44608,7 @@
         <v>45533</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44686,7 +44686,7 @@
         <v>46189</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>46188</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44832,7 +44832,7 @@
         <v>45635</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44905,7 +44905,7 @@
         <v>45155</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44983,7 +44983,7 @@
         <v>45159</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>44911</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45875</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>46195</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45290,7 +45290,7 @@
         <v>45875</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>46195</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>46195</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45875</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>46195</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45675,7 +45675,7 @@
         <v>46196</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>46196</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45554</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>46196</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45513</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46045,7 +46045,7 @@
         <v>46196</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46118,7 +46118,7 @@
         <v>45614</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46196</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>46196</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46342,7 +46342,7 @@
         <v>45568</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46415,7 +46415,7 @@
         <v>45559</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>46198</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>46198</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45596</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46722,7 +46722,7 @@
         <v>45628</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>46198</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>46198</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>46198</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>46198</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>46199</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45452</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>46198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47336,7 +47336,7 @@
         <v>45104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45609</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45579</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47565,7 +47565,7 @@
         <v>45737</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45216</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>46203</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45882</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45645</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47940,7 +47940,7 @@
         <v>45882</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48018,7 +48018,7 @@
         <v>45882</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>46184</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45589</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>46205</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48325,7 +48325,7 @@
         <v>45427</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>46204</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>46205</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45063</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>46204</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48705,7 +48705,7 @@
         <v>46251</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48783,7 +48783,7 @@
         <v>46251</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46252</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>46252</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45629</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>46251</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>46252</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>46252</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45715</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>46251</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45623</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49616,7 +49616,7 @@
         <v>45167</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46254</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46254</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49840,7 +49840,7 @@
         <v>45728</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>44673</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49986,7 +49986,7 @@
         <v>45434</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46213</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45159</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>45645</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>45583</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45642</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45763</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45740</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>44777</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>44693</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45226</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>46219</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>46219</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50980,7 +50980,7 @@
         <v>46219</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>46219</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45463</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45211</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44910</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45643</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>45135</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>46266</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>46220</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>46265</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45316</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46220</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>46262</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46220</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>46251</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52130,7 +52130,7 @@
         <v>46265</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45238</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>46265</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45230</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45832</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46265</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46266</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52656,7 +52656,7 @@
         <v>45327</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>44974</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45309</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>46267</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         <v>45163</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>46268</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>46267</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>46267</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53260,7 +53260,7 @@
         <v>45254</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45250</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>44749</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53479,7 +53479,7 @@
         <v>46269</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>46269</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>46269</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>46269</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>46241</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53864,7 +53864,7 @@
         <v>45462</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>46230</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54020,7 +54020,7 @@
         <v>44925</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54093,7 +54093,7 @@
         <v>45229</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54166,7 +54166,7 @@
         <v>45559</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54244,7 +54244,7 @@
         <v>46230</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>46275</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54400,7 +54400,7 @@
         <v>46275</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>46275</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>45484</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>46275</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45748</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54785,7 +54785,7 @@
         <v>46280</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>44685</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>46280</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>46237</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55082,7 +55082,7 @@
         <v>46234</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>46119</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45163</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>46234</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>46234</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45148</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>46238</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55613,7 +55613,7 @@
         <v>45740</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55686,7 +55686,7 @@
         <v>46281</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>46282</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>46282</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>46282</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>46282</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45589</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>46285</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56285,7 +56285,7 @@
         <v>46285</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56358,7 +56358,7 @@
         <v>46241</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56431,7 +56431,7 @@
         <v>46285</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56504,7 +56504,7 @@
         <v>45326</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56582,7 +56582,7 @@
         <v>46185</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>46286</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>46240</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>45405</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56879,7 +56879,7 @@
         <v>45520</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45560</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57035,7 +57035,7 @@
         <v>45560</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57113,7 +57113,7 @@
         <v>44915</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57191,7 +57191,7 @@
         <v>46241</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>44925</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>44925</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>45331</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>46285</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>46285</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>46241</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>46287</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>46288</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>46244</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>46244</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>44917</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58092,7 +58092,7 @@
         <v>45816</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>45560</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45560</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>46245</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46248</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>46219</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45540</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>45596</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58784,7 +58784,7 @@
         <v>45596</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>45622</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45463</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>45251</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59081,7 +59081,7 @@
         <v>46199</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>46248</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>45001</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>46246</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>44889</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45104</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>46247</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>45520</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59695,7 +59695,7 @@
         <v>44659</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>45338</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>44902</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45174</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45520</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60065,7 +60065,7 @@
         <v>45387</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45151</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>45210</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60299,7 +60299,7 @@
         <v>45565</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45175</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60455,7 +60455,7 @@
         <v>45057</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>45600</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60601,7 +60601,7 @@
         <v>45684</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60674,7 +60674,7 @@
         <v>45148</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60747,7 +60747,7 @@
         <v>45684</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60825,7 +60825,7 @@
         <v>44840</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45453</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60971,7 +60971,7 @@
         <v>45646</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61044,7 +61044,7 @@
         <v>45775</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61122,7 +61122,7 @@
         <v>44902</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>45559</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>45520</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>44860</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45460</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44559</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>45677</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45105</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45625</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45628</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61872,7 +61872,7 @@
         <v>45616</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45145</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>44925</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>44925</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>44479</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         <v>45261</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>45328</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62403,7 +62403,7 @@
         <v>45215</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45560</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62554,7 +62554,7 @@
         <v>45686</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62627,7 +62627,7 @@
         <v>45069</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45666</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62778,7 +62778,7 @@
         <v>45763</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62856,7 +62856,7 @@
         <v>44963</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62929,7 +62929,7 @@
         <v>45748</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         <v>44987</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63080,7 +63080,7 @@
         <v>45511</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63153,7 +63153,7 @@
         <v>45729</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45159</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45453</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45530</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63450,7 +63450,7 @@
         <v>45541</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45541</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45685</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63679,7 +63679,7 @@
         <v>45644</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63752,7 +63752,7 @@
         <v>45630</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>44944</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45701</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>44572</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>45776</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45776</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45777</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64278,7 +64278,7 @@
         <v>45777</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>44875</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64434,7 +64434,7 @@
         <v>45782</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>45783</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64590,7 +64590,7 @@
         <v>45785</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64663,7 +64663,7 @@
         <v>45460</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         <v>45296</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64814,7 +64814,7 @@
         <v>44463</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>44635</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>44607</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65038,7 +65038,7 @@
         <v>44603</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65116,7 +65116,7 @@
         <v>44713</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>44635</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65262,7 +65262,7 @@
         <v>45673</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>45392</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65413,7 +65413,7 @@
         <v>45249</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>44904</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65569,7 +65569,7 @@
         <v>45747</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65647,7 +65647,7 @@
         <v>45747</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65725,7 +65725,7 @@
         <v>45747</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65803,7 +65803,7 @@
         <v>45747</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65881,7 +65881,7 @@
         <v>45747</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65959,7 +65959,7 @@
         <v>45776</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66037,7 +66037,7 @@
         <v>45775</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66110,7 +66110,7 @@
         <v>45916</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66183,7 +66183,7 @@
         <v>46114</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66256,7 +66256,7 @@
         <v>46149</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46122</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>44788</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45863</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46198</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45457</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45217</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>45811</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45457</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46100</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44917</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45617</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45793</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>46083</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45825</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44924</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>46212</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45254</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45148</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45793</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44742</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45933</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>46070</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45737</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45230</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46114</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45170</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46164</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45385</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>46191</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>46198</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45630</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>45159</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46280</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45159</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>46246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>46248</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44949</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44943</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44693</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44652</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44559</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44714</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44802</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44715</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44872</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44473</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44614</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>44797</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44860</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44540</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>44721</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44803</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44854</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45728</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45551</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45644</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>45208</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45520</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45057</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45463</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45775</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44851</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45212</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45455</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45238</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45159</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45019</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44883</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>44902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45299</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46001</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>46002</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45167</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>46001</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>46002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>46006</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44777</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>46006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45104</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>46006</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45527</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46008</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>46009</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45148</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45296</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44889</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45460</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>46009</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>46009</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45583</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45309</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45533</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>44902</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44935</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44935</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45919</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45510</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>44971</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45896</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>46031</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>46031</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>45896</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45897</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45729</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44910</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44916</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>46035</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45898</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45163</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45905</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45511</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45909</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45793</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44652</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45796</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45671</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45320</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45794</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45721</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>45915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45912</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45915</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45518</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45912</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45912</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45912</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45915</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46049</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45523</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45069</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45919</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45567</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45159</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45918</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45919</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45805</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44868</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45240</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45807</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45807</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45924</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45924</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45148</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44962</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45929</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>46059</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45928</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45928</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45474</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45468</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45463</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>46065</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45740</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45811</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>46066</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44840</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45646</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45181</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>46070</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44673</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45938</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45019</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>46073</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>46072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46073</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45250</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>46073</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45810</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45330</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45944</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>46077</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45945</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45944</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>46076</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45944</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45155</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45811</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45063</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>46078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45946</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45946</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45947</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45950</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46079</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45103</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45104</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45946</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45251</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45723</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46083</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>46085</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45642</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45105</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45603</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44987</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45576</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45959</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45959</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45959</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45961</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45483</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45961</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45961</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45961</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45961</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45960</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>46091</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44559</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>46091</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45226</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44685</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45817</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45964</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45817</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45279</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45623</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45299</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>46097</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45434</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46099</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45609</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45973</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46099</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45513</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46100</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46101</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45513</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45714</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45520</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45525</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45979</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45978</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45148</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45979</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45979</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45979</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45686</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45460</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46107</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45980</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45819</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45980</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>46107</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45982</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45463</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45985</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45825</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45043</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>46113</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45825</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45219</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>46113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>46113</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44749</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46120</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46120</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45825</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45993</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46122</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>44794</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45993</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45560</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45560</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45995</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45994</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>46128</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45999</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45559</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45545</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46000</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>45831</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45537</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45506</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45831</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45829</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45832</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45706</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44644</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46134</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45832</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45835</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45835</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45835</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45834</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45835</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45187</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45316</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45175</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45387</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45838</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45537</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45161</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45841</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45511</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>44825</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45061</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45162</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45847</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45728</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45534</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44749</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45579</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45644</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44974</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45755</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45580</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44839</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>46139</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45863</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45553</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45560</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45114</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46136</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44924</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45145</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45838</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45861</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45861</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>45684</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45320</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45884</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45842</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45789</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45514</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>44963</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45453</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45643</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45247</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45867</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45539</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45867</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45674</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45114</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45616</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46140</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45005</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45114</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45868</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45511</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45685</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45737</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45427</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>45763</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45575</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45737</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45462</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45452</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>44491</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>45526</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45576</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45397</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>46153</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45019</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44552</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>46155</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>46077</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45887</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45635</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45739</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>46155</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45554</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45554</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45875</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>44917</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45163</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>45832</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>46160</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46161</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45163</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45841</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45559</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45616</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>46160</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45875</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45875</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>44494</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46162</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45645</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>46163</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45622</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45629</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>46167</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>44659</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>46169</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45159</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>44944</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>44886</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45537</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>45537</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44944</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45882</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>46171</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>44610</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>46174</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45331</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45882</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>46171</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45216</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>46171</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45882</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>46175</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45230</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>46177</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45250</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46177</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45748</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>46181</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>46181</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>46181</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45512</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45260</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45338</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46188</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45526</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45001</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45616</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45616</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>46185</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45630</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>46185</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45326</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>46189</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>44911</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>44925</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45771</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>46195</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>46195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>46196</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>46196</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>46196</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>45007</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>46196</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45596</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45540</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>46195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>46196</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46198</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>46198</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>44925</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44925</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>46198</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45225</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>46198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45135</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45597</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>46199</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>46184</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>46203</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46204</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>46204</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46206</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45453</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45646</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46205</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45244</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>44910</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>44973</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45625</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46213</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45405</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45425</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46265</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46262</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45554</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46265</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46220</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46220</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>46219</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45832</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46265</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45328</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>46219</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>46219</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>46219</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>46266</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50985,7 +50985,7 @@
         <v>44886</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>46267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>46265</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46267</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>46267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>46266</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>46268</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>44924</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46269</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45513</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45385</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>46269</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>46269</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46269</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45509</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>44845</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45229</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>45559</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45559</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>46230</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46230</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>44889</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45104</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>44818</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>46275</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>44902</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>46275</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         <v>46275</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46275</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>46234</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>46234</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>46234</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46119</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45596</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45420</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>44641</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>46280</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
         <v>46237</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>46280</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45719</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>46238</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>45569</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45232</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>45763</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>46281</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45538</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>46282</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>45537</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46282</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>44693</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46282</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45754</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45226</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45453</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>46240</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>46282</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>46282</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>45583</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45645</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55545,7 +55545,7 @@
         <v>45816</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45569</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55701,7 +55701,7 @@
         <v>46244</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45560</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55857,7 +55857,7 @@
         <v>46241</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45596</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56008,7 +56008,7 @@
         <v>45596</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>46241</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>46287</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>45677</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>46286</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>46185</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>46244</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45532</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>46285</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>46285</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>46285</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>46285</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         <v>46285</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56967,7 +56967,7 @@
         <v>45748</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>46245</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>46288</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57196,7 +57196,7 @@
         <v>45344</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>46246</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>45145</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45327</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45215</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>44881</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45267</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45737</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>46199</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45520</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>46247</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46248</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>45151</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46248</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>45541</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45541</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>45069</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>45559</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>45453</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>46251</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45113</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59013,7 +59013,7 @@
         <v>44971</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45329</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>45684</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>46252</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>46252</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59383,7 +59383,7 @@
         <v>46252</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>46252</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>46251</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>46251</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>44916</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>46196</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>44839</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>44925</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>46198</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>44614</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>44479</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45513</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>44860</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45740</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46241</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>45560</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45560</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>45254</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45734</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45665</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>46198</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45715</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>46297</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46297</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45740</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>44925</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>44925</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>46241</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>46219</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>46254</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46254</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46195</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>46251</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46251</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45518</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>45068</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>45559</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>45530</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62222,7 +62222,7 @@
         <v>45484</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>44565</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>44572</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>44925</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>45460</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>45568</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>45105</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62743,7 +62743,7 @@
         <v>45306</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>45261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45338</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45635</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45589</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>45589</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>45628</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>45628</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63357,7 +63357,7 @@
         <v>45453</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45453</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63513,7 +63513,7 @@
         <v>45754</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63586,7 +63586,7 @@
         <v>45614</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>45666</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63742,7 +63742,7 @@
         <v>45210</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45701</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>45600</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63966,7 +63966,7 @@
         <v>45643</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
         <v>45646</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64117,7 +64117,7 @@
         <v>45630</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64195,7 +64195,7 @@
         <v>45737</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45776</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         <v>45777</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45777</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64497,7 +64497,7 @@
         <v>45776</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>44875</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>45782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45783</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64804,7 +64804,7 @@
         <v>44463</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64877,7 +64877,7 @@
         <v>44635</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64950,7 +64950,7 @@
         <v>45673</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65028,7 +65028,7 @@
         <v>45392</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65101,7 +65101,7 @@
         <v>44607</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>44603</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>44713</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45249</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>44904</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65486,7 +65486,7 @@
         <v>44635</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65559,7 +65559,7 @@
         <v>45747</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>45747</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>45747</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45747</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65871,7 +65871,7 @@
         <v>45747</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65949,7 +65949,7 @@
         <v>45776</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66027,7 +66027,7 @@
         <v>45775</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66100,7 +66100,7 @@
         <v>45916</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>46114</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66246,7 +66246,7 @@
         <v>46149</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46122</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>44788</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45863</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46198</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45457</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45217</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45310</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>45811</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>45457</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45813</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46100</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44917</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45617</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45793</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45666</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>46083</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45155</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>45825</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>44924</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>46212</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>45254</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45148</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>45793</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>44742</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45933</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>46070</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45737</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45230</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46114</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45170</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>45832</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45867</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>46164</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45385</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>46191</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>46198</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>46203</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>45630</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         <v>45159</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46280</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45159</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>46246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>46248</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>45516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44949</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>44351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44635</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>44943</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44693</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>44652</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>44876</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>44488</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>44559</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44546</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>44714</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44879</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44797</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44875</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44500</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44802</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44715</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44872</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44872</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>44473</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>44614</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>44581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>44797</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44860</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44540</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>44721</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44803</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>44854</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14095,7 +14095,7 @@
         <v>45728</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>44915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>44490</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45551</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45644</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>45208</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45517</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45520</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45057</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45463</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>45775</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44851</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45212</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45455</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45510</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45238</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45159</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45019</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45785</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>44883</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>44902</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>45299</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>46000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>46001</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>46002</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45167</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>46001</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>46002</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>46006</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44777</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>46006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45104</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45887</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>46006</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>45527</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46008</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>46009</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>46009</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45148</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45296</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>44889</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45460</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         <v>46009</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>46009</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45583</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17518,7 +17518,7 @@
         <v>45309</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45533</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>45616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>44902</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44935</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>44935</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45919</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45510</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>44971</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45896</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>46031</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>46031</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>45896</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45896</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45897</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45901</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45729</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44910</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44916</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>46035</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45898</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45163</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45905</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45511</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45909</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>45602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45793</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44652</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45796</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45671</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45320</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45915</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45794</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45721</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>45915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45912</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>45915</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45915</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>45915</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45518</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45912</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21449,7 +21449,7 @@
         <v>45912</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45912</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45915</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45915</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46049</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45523</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45069</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45916</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45919</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45567</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45159</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45918</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45919</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22491,7 +22491,7 @@
         <v>45805</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44868</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45240</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45807</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45807</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>44882</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45924</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>45924</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45148</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>44962</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23236,7 +23236,7 @@
         <v>45929</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>46059</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45928</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45928</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45474</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45468</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45463</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>46065</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45740</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45811</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>46066</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44840</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45646</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45181</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>46070</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>44673</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45938</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45019</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>46073</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>46072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45939</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46073</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45250</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>46073</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45810</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>45330</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45944</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>46077</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45945</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>45944</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>46076</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25846,7 +25846,7 @@
         <v>45944</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>45155</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45811</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45063</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26221,7 +26221,7 @@
         <v>46078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45946</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45946</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>45947</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>45950</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46079</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46084</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45103</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45104</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26966,7 +26966,7 @@
         <v>45952</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45946</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45251</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45723</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>46083</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>46085</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45642</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45105</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45603</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44987</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45576</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45959</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45959</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45959</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45961</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>45483</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45961</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45961</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45961</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45961</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45961</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45960</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>46091</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45961</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>44559</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>46091</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45226</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>44685</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45817</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29410,7 +29410,7 @@
         <v>45964</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45817</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45279</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45623</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45299</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>46097</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45434</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>46099</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45609</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45973</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46099</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>45513</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>46100</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46101</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45513</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45714</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45520</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45525</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45979</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45978</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45148</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45979</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45979</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>45978</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45979</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45686</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45685</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45460</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>46107</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45980</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45819</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45980</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>46107</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32216,7 +32216,7 @@
         <v>45982</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45463</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45114</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45985</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
         <v>45825</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>45043</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>46113</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>45825</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45219</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>46113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>46113</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>46113</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44749</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>46120</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>46120</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45825</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45993</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46122</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>44794</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>45993</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45560</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>45560</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45995</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34383,7 +34383,7 @@
         <v>45827</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34461,7 +34461,7 @@
         <v>45994</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34534,7 +34534,7 @@
         <v>46128</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45999</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45559</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45545</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46000</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>45831</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45537</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45506</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45831</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45829</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45832</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>46134</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45706</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>44644</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>46134</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45832</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45835</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45835</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45835</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45834</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45835</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>45187</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45565</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45316</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45175</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45387</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45838</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45537</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45161</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45841</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36902,7 +36902,7 @@
         <v>45511</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>44825</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         <v>45061</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37121,7 +37121,7 @@
         <v>45162</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37199,7 +37199,7 @@
         <v>45847</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45728</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45534</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44749</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45579</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45644</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>44974</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45755</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45580</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>44839</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>46139</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45863</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45553</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45560</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45114</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46136</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44924</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>45145</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45838</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>45861</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45861</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>45684</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45320</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45884</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45842</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45789</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45514</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>44963</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>45453</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45643</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39484,7 +39484,7 @@
         <v>45247</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45867</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45539</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>45867</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45674</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45114</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45616</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46140</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45005</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40161,7 +40161,7 @@
         <v>45114</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>45868</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45511</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45155</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45685</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>45737</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45427</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>45763</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>45575</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40828,7 +40828,7 @@
         <v>45737</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45462</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45452</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>44491</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>45526</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45576</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45397</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>46153</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45019</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44552</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>46155</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>46077</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45887</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45635</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>45739</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>46155</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45554</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45554</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45875</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>44917</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>45163</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>45832</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>46160</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46161</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45163</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45841</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45559</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45616</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>46160</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45875</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45875</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>44494</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46162</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45645</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>46163</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45622</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45629</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>46167</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>44659</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>46169</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45159</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>44944</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>44886</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45537</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>45537</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>44944</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45882</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>46171</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>44610</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>46174</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44603,7 +44603,7 @@
         <v>45331</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44681,7 +44681,7 @@
         <v>45882</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44759,7 +44759,7 @@
         <v>46171</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45216</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>46171</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45882</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45071,7 +45071,7 @@
         <v>46175</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45230</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>46177</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>45250</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45373,7 +45373,7 @@
         <v>46177</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45748</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45529,7 +45529,7 @@
         <v>46181</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45607,7 +45607,7 @@
         <v>46181</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>46181</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>45512</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45260</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45338</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46188</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45526</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45001</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45616</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46357,7 +46357,7 @@
         <v>45616</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>46185</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45630</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>46185</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45326</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46747,7 +46747,7 @@
         <v>46189</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>44911</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46903,7 +46903,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>44925</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45771</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>46195</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>46195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>46196</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47356,7 +47356,7 @@
         <v>46196</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>46196</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47502,7 +47502,7 @@
         <v>45007</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47575,7 +47575,7 @@
         <v>46196</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45596</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47726,7 +47726,7 @@
         <v>45540</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>46195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47882,7 +47882,7 @@
         <v>46196</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47955,7 +47955,7 @@
         <v>46198</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>46198</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48111,7 +48111,7 @@
         <v>44925</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48184,7 +48184,7 @@
         <v>44925</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>46198</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48340,7 +48340,7 @@
         <v>45225</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48413,7 +48413,7 @@
         <v>46198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45135</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45597</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>46199</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>46184</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>46203</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>46204</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>46204</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46206</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45453</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45646</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46205</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>45244</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>44910</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>44973</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45625</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46213</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45405</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45425</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46265</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46262</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45554</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46265</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46220</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46220</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>46219</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45832</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46265</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45328</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>46219</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>46219</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>46219</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>46266</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50985,7 +50985,7 @@
         <v>44886</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51058,7 +51058,7 @@
         <v>46267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>46265</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>46267</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>46267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>46266</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>46268</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>44924</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51589,7 +51589,7 @@
         <v>46269</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45513</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45385</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>46269</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>46269</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>46269</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45509</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>44845</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>45229</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>45559</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45559</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>46230</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46230</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52583,7 +52583,7 @@
         <v>44889</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>45104</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>44818</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>46275</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>44902</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>46275</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53041,7 +53041,7 @@
         <v>46275</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46275</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53197,7 +53197,7 @@
         <v>46234</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>46234</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53353,7 +53353,7 @@
         <v>46234</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46119</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45596</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45420</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53655,7 +53655,7 @@
         <v>44641</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>46280</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53801,7 +53801,7 @@
         <v>46237</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>46280</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45719</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>46238</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>45569</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45232</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54332,7 +54332,7 @@
         <v>45763</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>46281</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45538</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>46282</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>45537</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>46282</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>44693</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46282</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45754</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>45226</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>45453</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>46240</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>46282</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>46282</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>45583</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45645</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55545,7 +55545,7 @@
         <v>45816</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45569</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55701,7 +55701,7 @@
         <v>46244</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45560</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55857,7 +55857,7 @@
         <v>46241</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55935,7 +55935,7 @@
         <v>45596</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56008,7 +56008,7 @@
         <v>45596</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>46241</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56159,7 +56159,7 @@
         <v>46287</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>45677</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56305,7 +56305,7 @@
         <v>46286</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56378,7 +56378,7 @@
         <v>46185</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56451,7 +56451,7 @@
         <v>46244</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56529,7 +56529,7 @@
         <v>45532</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>46285</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56675,7 +56675,7 @@
         <v>46285</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>46285</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>46285</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         <v>46285</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56967,7 +56967,7 @@
         <v>45748</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57045,7 +57045,7 @@
         <v>46245</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>46288</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57196,7 +57196,7 @@
         <v>45344</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>46246</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>45145</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45327</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57498,7 +57498,7 @@
         <v>45215</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>44881</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57644,7 +57644,7 @@
         <v>45267</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>45737</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>46199</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45520</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58019,7 +58019,7 @@
         <v>46247</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58097,7 +58097,7 @@
         <v>45211</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58170,7 +58170,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>46248</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>45151</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46248</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>45541</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>45541</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>45069</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>45559</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>45453</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58862,7 +58862,7 @@
         <v>46251</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45113</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59013,7 +59013,7 @@
         <v>44971</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45329</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>45684</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>46252</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>46252</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59383,7 +59383,7 @@
         <v>46252</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>46252</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59534,7 +59534,7 @@
         <v>46251</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59612,7 +59612,7 @@
         <v>46251</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>44916</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>46196</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>44839</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>44925</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>46198</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>44614</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>44479</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45513</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>44860</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45740</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46241</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>45560</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>45560</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>45254</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45734</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45665</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>46198</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45715</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>46297</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46297</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>45740</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>44925</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61326,7 +61326,7 @@
         <v>44925</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61399,7 +61399,7 @@
         <v>46241</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>46219</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>46254</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46254</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46195</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61769,7 +61769,7 @@
         <v>46251</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46251</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45518</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>45068</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>45559</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>45530</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62222,7 +62222,7 @@
         <v>45484</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>44565</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>44572</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62441,7 +62441,7 @@
         <v>44925</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62514,7 +62514,7 @@
         <v>45460</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62592,7 +62592,7 @@
         <v>45568</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62665,7 +62665,7 @@
         <v>45105</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62743,7 +62743,7 @@
         <v>45306</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>45261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45338</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45635</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45589</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>45589</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>45628</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>45628</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63357,7 +63357,7 @@
         <v>45453</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45453</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63513,7 +63513,7 @@
         <v>45754</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63586,7 +63586,7 @@
         <v>45614</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>45666</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63742,7 +63742,7 @@
         <v>45210</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45701</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>45600</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63966,7 +63966,7 @@
         <v>45643</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
         <v>45646</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64117,7 +64117,7 @@
         <v>45630</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64195,7 +64195,7 @@
         <v>45737</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45776</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         <v>45777</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64419,7 +64419,7 @@
         <v>45777</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64497,7 +64497,7 @@
         <v>45776</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>44875</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>45782</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45783</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64804,7 +64804,7 @@
         <v>44463</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64877,7 +64877,7 @@
         <v>44635</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64950,7 +64950,7 @@
         <v>45673</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65028,7 +65028,7 @@
         <v>45392</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65101,7 +65101,7 @@
         <v>44607</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>44603</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>44713</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45249</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>44904</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65486,7 +65486,7 @@
         <v>44635</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65559,7 +65559,7 @@
         <v>45747</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>45747</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>45747</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45747</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65871,7 +65871,7 @@
         <v>45747</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65949,7 +65949,7 @@
         <v>45776</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66027,7 +66027,7 @@
         <v>45775</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66100,7 +66100,7 @@
         <v>45916</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66173,7 +66173,7 @@
         <v>46114</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66246,7 +66246,7 @@
         <v>46149</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45863</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46122</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44788</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46198</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45457</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46176</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45611</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45217</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45457</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>45811</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45842</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46100</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45793</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45825</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45666</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44924</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>46083</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46212</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45254</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>46301</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45630</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45516</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44949</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45793</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45385</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45230</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45933</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45944</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45832</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45867</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45159</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45436</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>46077</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>45737</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>46181</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>46191</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>46198</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>46203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>46280</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>46246</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>46248</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45159</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44872</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44652</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44488</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44797</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44500</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44715</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44685</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44797</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>44540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44511</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44537</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>44872</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44536</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44600</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44679</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44711</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44721</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44865</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44509</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44860</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44872</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>44743</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45069</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45684</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>44854</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>44851</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>45684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44840</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45453</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44644</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45646</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45390</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>44818</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44902</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45559</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45520</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45597</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44860</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44794</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45740</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44490</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45460</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45728</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45734</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45553</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44559</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44839</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45677</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>44910</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45560</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45512</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>44825</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45105</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45625</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45628</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45225</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45616</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45145</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45559</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45455</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45559</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45299</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44925</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44925</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45420</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>44479</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45453</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45576</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45453</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45723</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45320</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45644</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45114</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45576</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45719</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45453</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45532</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45261</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45208</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45754</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45328</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44845</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45215</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45397</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45560</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45686</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45666</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44962</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45105</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45306</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45763</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45509</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44963</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45247</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45748</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45453</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45267</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45463</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44987</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45511</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44491</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45729</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45537</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45545</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45537</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45279</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45887</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44935</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44935</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45602</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45159</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45453</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45511</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44881</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45510</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45506</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45537</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>44902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44494</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45803</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45896</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45897</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45530</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45541</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45541</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45644</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45630</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44944</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45701</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45510</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45329</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>44973</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45575</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45537</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45538</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45905</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44572</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45909</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45776</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45776</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45425</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45616</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45527</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45777</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45912</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45754</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45912</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45777</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>45912</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>44916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44875</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45911</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45019</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45782</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45915</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45916</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45737</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45915</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45783</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45915</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45569</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45915</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45915</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45916</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45148</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45523</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45145</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45918</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45513</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44924</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45616</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45616</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45616</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45919</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45518</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45518</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45525</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45533</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45919</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44552</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45635</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45155</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45159</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45924</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45924</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45460</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45240</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45296</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45513</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45232</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45928</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45928</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45554</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44652</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45513</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45671</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44614</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45793</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45320</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>45614</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45794</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45568</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45517</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45559</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45596</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45628</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45796</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45721</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45554</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45452</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44971</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45104</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45609</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45737</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45216</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45385</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45212</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45645</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45589</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45936</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45583</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>44916</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44610</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45427</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45063</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45567</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>44868</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45629</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45569</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45526</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44641</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45715</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45807</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45181</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45807</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45684</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45226</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45330</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45623</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45630</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45810</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>44944</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45167</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45939</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45811</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45944</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45944</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45944</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45945</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45603</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45946</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45811</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45946</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45817</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45260</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45947</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45728</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>44673</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45817</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45483</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45950</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>45434</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45820</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45159</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45645</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45583</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45825</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45019</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45952</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45642</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45825</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45952</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45763</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45827</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45831</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45832</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45832</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45829</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45299</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45740</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45831</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45946</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44924</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45959</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45959</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45959</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45960</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45219</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45834</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45643</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44777</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>44693</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45226</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45961</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45961</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45961</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45964</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45961</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45961</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45961</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45964</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45835</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45835</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45835</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45961</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45838</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45835</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45961</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45961</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44925</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>44971</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>45019</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45163</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45463</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45841</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45211</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>44910</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45971</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45643</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45135</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45973</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45316</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45068</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45973</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45230</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45847</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45327</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>44974</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45005</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45114</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45309</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45163</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45978</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>45861</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45114</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45861</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45978</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45254</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45103</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45104</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45250</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45868</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>44749</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>45867</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45867</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>44565</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45979</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>45714</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45646</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45980</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45685</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45979</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45462</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45979</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45665</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>44925</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45646</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45980</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45980</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45979</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45875</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45229</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45980</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45875</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45875</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45706</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45513</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45737</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>45739</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>45484</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>45882</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45882</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45554</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45882</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44749</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45982</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45748</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46099</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>44886</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>44685</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45526</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46099</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45985</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>46101</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>46100</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45163</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>45737</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45250</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45148</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45043</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45740</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>46107</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>46107</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>45988</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45589</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>45755</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46111</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>46112</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>46113</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>46113</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45534</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45326</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>46113</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46068,7 +46068,7 @@
         <v>45405</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45520</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>45560</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45560</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>46120</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>44915</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45993</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45993</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45993</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46120</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>44925</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>44925</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46122</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45331</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45994</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45995</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45537</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46000</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46000</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45999</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>46001</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>44917</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46128</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>46001</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>46002</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45560</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46002</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>46134</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46006</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>46006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46006</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>46008</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45244</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>45540</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45596</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45596</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45622</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45463</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45251</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>46009</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>46009</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46136</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>46009</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45001</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>46009</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>44889</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45842</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45104</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45674</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>45919</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>44659</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45338</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>44902</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>45174</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45162</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>46031</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>46031</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45789</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>46031</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45187</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45387</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>45838</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>45151</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45210</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46035</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45565</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>46041</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45175</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>46139</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>46140</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45884</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45863</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45514</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45161</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>45061</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45057</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45600</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>45453</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45511</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46049</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45539</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>45616</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>46059</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45468</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45474</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>46059</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52614,7 +52614,7 @@
         <v>46065</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>46066</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>46070</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>46072</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>46073</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>46073</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>46076</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>46073</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>46153</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>46077</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>46079</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>46078</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>46083</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45635</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>46084</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53744,7 +53744,7 @@
         <v>46155</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53817,7 +53817,7 @@
         <v>46085</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53890,7 +53890,7 @@
         <v>46155</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53968,7 +53968,7 @@
         <v>46084</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>45887</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>46077</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>46160</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>46091</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>46091</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>46160</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>45841</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45559</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46161</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>46097</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45832</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>46163</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46162</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46167</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>46169</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>46171</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>46171</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46171</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>46174</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46175</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>46177</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>46177</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>46181</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>46181</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>46181</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55946,7 +55946,7 @@
         <v>46185</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>46184</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>46185</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>46189</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>46189</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46188</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>44911</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56477,7 +56477,7 @@
         <v>46195</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46195</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>46195</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46196</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>46196</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>46196</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57003,7 +57003,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>46198</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>46198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>46199</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>46198</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>46203</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>46184</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         <v>46205</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>46204</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57690,7 +57690,7 @@
         <v>46204</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>46206</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57846,7 +57846,7 @@
         <v>46213</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>46219</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>46219</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46219</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58158,7 +58158,7 @@
         <v>46219</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>46266</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         <v>46220</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>46265</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>46220</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>46265</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58616,7 +58616,7 @@
         <v>46265</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>45832</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>46265</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58840,7 +58840,7 @@
         <v>46266</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>46267</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>46268</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>46267</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>46267</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59220,7 +59220,7 @@
         <v>46269</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59298,7 +59298,7 @@
         <v>46269</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59376,7 +59376,7 @@
         <v>46269</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59454,7 +59454,7 @@
         <v>46269</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>46230</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59610,7 +59610,7 @@
         <v>45559</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>46230</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>46275</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>46275</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>46275</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60000,7 +60000,7 @@
         <v>46275</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>46280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>46237</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60302,7 +60302,7 @@
         <v>46234</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>46119</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>46234</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>46234</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>46238</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>46281</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60765,7 +60765,7 @@
         <v>46282</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>46282</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>46282</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>46282</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>46282</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>46285</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61208,7 +61208,7 @@
         <v>46285</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>46285</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>46185</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61427,7 +61427,7 @@
         <v>46286</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>46240</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>46241</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>46285</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61729,7 +61729,7 @@
         <v>46285</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>46241</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>46287</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>46288</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>46244</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62104,7 +62104,7 @@
         <v>46244</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62182,7 +62182,7 @@
         <v>45816</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62260,7 +62260,7 @@
         <v>46245</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62338,7 +62338,7 @@
         <v>46199</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62411,7 +62411,7 @@
         <v>46246</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>46247</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>45520</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>46248</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>46293</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62801,7 +62801,7 @@
         <v>46248</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         <v>46293</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>46251</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63113,7 +63113,7 @@
         <v>46251</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>46252</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>46252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>46252</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>46251</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>46300</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>46241</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>46297</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>46254</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>46195</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>46300</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>46219</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64087,7 +64087,7 @@
         <v>46241</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64160,7 +64160,7 @@
         <v>46198</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>44839</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>46196</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>46251</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>46251</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>46297</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>46198</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>46301</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>45825</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>46262</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>44463</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64983,7 +64983,7 @@
         <v>44635</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>44607</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>44603</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65212,7 +65212,7 @@
         <v>44713</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>44635</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>45673</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>45392</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45249</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>44904</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45747</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45747</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45747</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65899,7 +65899,7 @@
         <v>45747</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65977,7 +65977,7 @@
         <v>45747</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45776</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66133,7 +66133,7 @@
         <v>45775</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45916</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66279,7 +66279,7 @@
         <v>46114</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66352,7 +66352,7 @@
         <v>46149</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>45863</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46122</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>44788</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>46198</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45457</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46266</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45505</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>46176</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45740</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>45611</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45217</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>45457</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>45811</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>46189</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45813</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45842</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46100</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>46226</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45793</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45617</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45825</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>45155</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45666</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>44924</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>46083</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46212</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45254</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>46301</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45630</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45516</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44949</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45793</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45385</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45230</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45933</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45944</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>45832</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>45170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>44742</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45867</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>45159</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8740,7 +8740,7 @@
         <v>45875</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45436</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>46114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>46077</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>45737</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>46181</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>46191</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>46198</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>46203</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9947,7 +9947,7 @@
         <v>46280</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>46246</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>46248</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45159</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44872</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44652</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44488</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44797</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44500</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44715</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44685</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44797</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>44540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>44511</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>44537</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>44872</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44536</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>44600</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44679</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44713</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44711</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>44721</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44865</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44509</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44860</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44872</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>44743</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
         <v>44614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45069</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45684</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>44854</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14274,7 +14274,7 @@
         <v>44851</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14420,7 +14420,7 @@
         <v>44886</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45771</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14571,7 +14571,7 @@
         <v>45684</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44840</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45453</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44644</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45646</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>44925</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>45390</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>44818</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>44902</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45559</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45520</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>45597</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44860</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44794</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45740</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44490</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45460</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45728</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45734</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45553</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44559</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>44839</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45677</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>44910</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45560</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45512</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>44825</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45105</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>45625</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45628</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45460</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         <v>45225</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>45616</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45145</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17332,7 +17332,7 @@
         <v>45559</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17410,7 +17410,7 @@
         <v>45455</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45559</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45299</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44925</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44925</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45420</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>44479</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45453</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>44902</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45576</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45113</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45453</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45723</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45320</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45644</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45114</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45576</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45719</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45453</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>45532</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45261</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45208</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45344</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45754</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45328</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44845</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45215</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45397</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45560</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>45686</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45069</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19801,7 +19801,7 @@
         <v>45666</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44962</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45105</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45306</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45763</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45509</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44963</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45247</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45748</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>45453</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45267</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45463</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44987</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45511</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45580</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>44491</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45729</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45537</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45545</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45537</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>44882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45279</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45887</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>44935</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44935</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>44935</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45602</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45159</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45453</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45511</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44881</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44883</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45510</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45506</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45537</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
         <v>44902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>44494</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45803</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>45894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45896</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>45896</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45898</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45897</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45530</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45541</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45541</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45644</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45630</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44944</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45701</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45510</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45329</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>44973</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>45575</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45537</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45538</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45905</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44572</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45909</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45776</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45776</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45425</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45616</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45527</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45911</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45777</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45912</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>45754</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45912</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45777</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>45912</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>44916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>44875</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45911</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>45019</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45782</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>45915</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45916</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45737</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45915</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45915</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45915</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45783</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>45915</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>45569</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>45915</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>45915</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45916</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45148</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45523</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>45145</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45918</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45513</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44924</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45616</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45616</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45616</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45919</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>44942</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45518</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45518</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45525</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45785</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45533</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45919</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44552</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45635</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45155</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45159</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28700,7 +28700,7 @@
         <v>45007</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>45924</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45924</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45460</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45240</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45296</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45513</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45232</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45928</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45928</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45554</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44652</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45513</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>45671</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44614</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45793</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45320</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>45614</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45794</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45568</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45517</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45559</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45596</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45628</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45796</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45721</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45554</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>45452</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30872,7 +30872,7 @@
         <v>44971</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45104</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31018,7 +31018,7 @@
         <v>45609</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45579</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45737</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31247,7 +31247,7 @@
         <v>45216</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45385</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>45212</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31476,7 +31476,7 @@
         <v>45645</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>45589</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45936</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45583</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>44916</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44610</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45427</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45063</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45567</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45938</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32226,7 +32226,7 @@
         <v>45805</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>44868</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45629</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45569</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32528,7 +32528,7 @@
         <v>45526</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32606,7 +32606,7 @@
         <v>44641</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32679,7 +32679,7 @@
         <v>45715</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>45807</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45181</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>45807</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45684</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45226</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33132,7 +33132,7 @@
         <v>45330</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33205,7 +33205,7 @@
         <v>45623</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33278,7 +33278,7 @@
         <v>45630</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45810</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>44944</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45167</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45939</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45811</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45944</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45944</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45944</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45945</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45603</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45946</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45811</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45946</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45817</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45260</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45947</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45728</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>44673</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45817</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45483</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45950</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34929,7 +34929,7 @@
         <v>45434</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45819</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>45820</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>45159</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45645</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45583</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>45825</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45019</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45952</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45642</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>45825</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45952</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>45763</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45827</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>45831</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45832</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45832</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>45829</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45299</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45740</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45831</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>45946</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44924</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45959</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45959</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45959</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45960</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45219</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45834</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45643</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44777</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>44693</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45226</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45961</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45961</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45961</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45964</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45961</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45961</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45961</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45964</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45835</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45835</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45835</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45961</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45838</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>45835</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45961</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45961</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>44925</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>44971</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         <v>45019</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45163</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45463</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45841</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45211</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>44910</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45971</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45643</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45135</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45973</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39595,7 +39595,7 @@
         <v>45316</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45155</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45068</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45973</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>45230</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45847</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45327</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>44974</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45005</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45114</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>45309</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>45163</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45978</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>45861</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45114</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>45861</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>45978</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45254</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45103</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41100,7 +41100,7 @@
         <v>45104</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45250</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45868</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>44749</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>45867</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45867</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>44565</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45979</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>45714</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41782,7 +41782,7 @@
         <v>45646</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>45980</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45685</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45979</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45462</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45979</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         <v>45665</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>44925</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42381,7 +42381,7 @@
         <v>45646</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>45980</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>45980</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45979</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45875</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>45229</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>45980</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>45875</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45875</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45706</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45513</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45737</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>45739</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>45484</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>45882</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45882</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>45554</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>45882</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43750,7 +43750,7 @@
         <v>44749</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>45982</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45748</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46099</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>44886</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>44685</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45526</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46099</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45985</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>46101</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45985</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>46100</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45163</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44719,7 +44719,7 @@
         <v>45737</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>45250</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45148</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45043</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45011,7 +45011,7 @@
         <v>45740</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45084,7 +45084,7 @@
         <v>46107</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>46107</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>45988</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45589</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45386,7 +45386,7 @@
         <v>45755</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>46111</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>46112</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>46113</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45693,7 +45693,7 @@
         <v>46113</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45766,7 +45766,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45534</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45326</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45990,7 +45990,7 @@
         <v>46113</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46068,7 +46068,7 @@
         <v>45405</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>45520</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46219,7 +46219,7 @@
         <v>45560</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45560</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>46120</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>44915</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45993</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
         <v>45993</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45993</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46120</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>44925</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>44925</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46122</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47047,7 +47047,7 @@
         <v>45331</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45994</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>45995</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45537</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>46000</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>46000</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45999</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>46001</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47646,7 +47646,7 @@
         <v>44917</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>46128</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47797,7 +47797,7 @@
         <v>46001</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>46002</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45560</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46002</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>46134</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46006</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>46006</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46006</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48474,7 +48474,7 @@
         <v>46008</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45244</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48620,7 +48620,7 @@
         <v>45540</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>45596</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45596</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48844,7 +48844,7 @@
         <v>45622</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45463</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45251</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>46009</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>46009</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46136</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>46009</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>45001</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>46009</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>44889</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49584,7 +49584,7 @@
         <v>45842</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45104</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45674</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>45919</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>44659</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45338</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>44902</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>45174</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>45162</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50261,7 +50261,7 @@
         <v>46031</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>46031</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45789</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50485,7 +50485,7 @@
         <v>46031</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45187</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>45387</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>45838</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>45151</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45210</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46035</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45565</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>46041</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45175</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>46139</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>46140</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45884</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51474,7 +51474,7 @@
         <v>45863</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51552,7 +51552,7 @@
         <v>45514</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51630,7 +51630,7 @@
         <v>45161</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>45061</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>45057</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51854,7 +51854,7 @@
         <v>45600</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51927,7 +51927,7 @@
         <v>45453</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45511</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52078,7 +52078,7 @@
         <v>46049</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52151,7 +52151,7 @@
         <v>45539</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52224,7 +52224,7 @@
         <v>45616</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>46059</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45468</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45474</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>46059</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52614,7 +52614,7 @@
         <v>46065</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52692,7 +52692,7 @@
         <v>46066</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>46070</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>46072</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>46073</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>46073</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>46076</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>46073</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>46153</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53291,7 +53291,7 @@
         <v>46077</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53364,7 +53364,7 @@
         <v>46079</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53437,7 +53437,7 @@
         <v>46078</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>46083</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45635</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>46084</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53744,7 +53744,7 @@
         <v>46155</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53817,7 +53817,7 @@
         <v>46085</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53890,7 +53890,7 @@
         <v>46155</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53968,7 +53968,7 @@
         <v>46084</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>45887</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>46077</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>46160</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>46091</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>46091</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>46160</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>45841</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45559</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46161</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>46097</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>45832</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>46163</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46162</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46167</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>46169</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>46171</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>46171</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46171</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>46174</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46175</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>46177</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>46177</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>46181</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>46181</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55868,7 +55868,7 @@
         <v>46181</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55946,7 +55946,7 @@
         <v>46185</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>46184</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56097,7 +56097,7 @@
         <v>46185</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>46189</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56253,7 +56253,7 @@
         <v>46189</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46188</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56399,7 +56399,7 @@
         <v>44911</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56477,7 +56477,7 @@
         <v>46195</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46195</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>46195</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46196</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>46196</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>46196</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57003,7 +57003,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>46198</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>46198</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>46199</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>46198</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>46203</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>46184</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         <v>46205</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>46204</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57690,7 +57690,7 @@
         <v>46204</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>46206</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57846,7 +57846,7 @@
         <v>46213</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>46219</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>46219</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46219</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58158,7 +58158,7 @@
         <v>46219</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>46266</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         <v>46220</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>46265</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>46220</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>46265</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58616,7 +58616,7 @@
         <v>46265</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>45832</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>46265</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58840,7 +58840,7 @@
         <v>46266</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>46267</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>46268</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>46267</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59142,7 +59142,7 @@
         <v>46267</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59220,7 +59220,7 @@
         <v>46269</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59298,7 +59298,7 @@
         <v>46269</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59376,7 +59376,7 @@
         <v>46269</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59454,7 +59454,7 @@
         <v>46269</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>46230</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59610,7 +59610,7 @@
         <v>45559</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>46230</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>46275</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>46275</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59922,7 +59922,7 @@
         <v>46275</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60000,7 +60000,7 @@
         <v>46275</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>46280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>46280</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>46237</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60302,7 +60302,7 @@
         <v>46234</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>46119</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60458,7 +60458,7 @@
         <v>46234</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>46234</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>46238</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60687,7 +60687,7 @@
         <v>46281</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60765,7 +60765,7 @@
         <v>46282</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60843,7 +60843,7 @@
         <v>46282</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         <v>46282</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>46282</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>46282</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61135,7 +61135,7 @@
         <v>46285</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61208,7 +61208,7 @@
         <v>46285</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>46285</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>46185</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61427,7 +61427,7 @@
         <v>46286</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>46240</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>46241</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>46285</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61729,7 +61729,7 @@
         <v>46285</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61802,7 +61802,7 @@
         <v>46241</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61880,7 +61880,7 @@
         <v>46287</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61953,7 +61953,7 @@
         <v>46288</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>46244</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62104,7 +62104,7 @@
         <v>46244</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62182,7 +62182,7 @@
         <v>45816</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62260,7 +62260,7 @@
         <v>46245</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62338,7 +62338,7 @@
         <v>46199</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62411,7 +62411,7 @@
         <v>46246</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>46247</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62567,7 +62567,7 @@
         <v>45520</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>46248</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>46293</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62801,7 +62801,7 @@
         <v>46248</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         <v>46293</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>46251</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63113,7 +63113,7 @@
         <v>46251</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>46252</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>46252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>46252</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>46251</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>46300</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>46241</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>46297</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>46254</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>46195</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>46300</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>46219</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64087,7 +64087,7 @@
         <v>46241</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64160,7 +64160,7 @@
         <v>46198</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>44839</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64311,7 +64311,7 @@
         <v>46196</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>46251</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64462,7 +64462,7 @@
         <v>46251</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64540,7 +64540,7 @@
         <v>46297</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>46198</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64691,7 +64691,7 @@
         <v>46301</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64764,7 +64764,7 @@
         <v>45825</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64837,7 +64837,7 @@
         <v>46262</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64910,7 +64910,7 @@
         <v>44463</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64983,7 +64983,7 @@
         <v>44635</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>44607</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>44603</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65212,7 +65212,7 @@
         <v>44713</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>44635</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>45673</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>45392</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45249</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>44904</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45747</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45747</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45747</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65899,7 +65899,7 @@
         <v>45747</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65977,7 +65977,7 @@
         <v>45747</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45776</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66133,7 +66133,7 @@
         <v>45775</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66206,7 +66206,7 @@
         <v>45916</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66279,7 +66279,7 @@
         <v>46114</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66352,7 +66352,7 @@
         <v>46149</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46198</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>46122</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45457</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45863</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45505</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45217</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45457</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>46189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>46241</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>45811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>46100</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>46226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46245</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45842</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45617</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45155</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44924</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>46083</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46212</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45254</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46301</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45793</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44742</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45230</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45170</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45944</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45436</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>46164</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45385</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>46181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>46077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45737</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>46191</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45630</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>46198</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>46114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>45159</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46246</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>46248</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45516</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44949</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45159</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45793</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45832</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45867</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44872</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44652</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44488</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44797</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44500</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44715</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44614</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>44797</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>44581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44860</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44540</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>44721</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>44684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44803</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>44854</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>44915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45453</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45644</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45551</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45208</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45517</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45520</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44851</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45463</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45212</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45455</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45238</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45510</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45159</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44883</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45299</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45019</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45167</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45104</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>44777</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45527</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45148</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45583</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45309</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44942</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44935</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>44935</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44935</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45533</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44971</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45729</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44910</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44916</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45721</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45518</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45159</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45240</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44882</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44962</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45148</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45740</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44673</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44840</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45646</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45019</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45250</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45155</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45063</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45103</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45251</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45723</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>44987</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45576</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45642</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44559</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44685</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45226</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45279</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45434</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45299</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45623</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45609</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45513</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45463</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45520</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45525</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45148</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45513</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45714</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45114</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45686</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45685</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45460</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45887</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45061</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45219</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44749</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44794</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>46139</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45863</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45560</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45559</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45545</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45510</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45803</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45506</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45894</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46136</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45896</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45838</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45896</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45896</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45897</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45901</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45706</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45884</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45842</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45789</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45514</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44644</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45539</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45674</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45616</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45511</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45565</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45316</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45905</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45175</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45909</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45387</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45537</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45915</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45915</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45912</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45915</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45915</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45915</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45912</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45912</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45915</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45523</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44825</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45919</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45918</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45728</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45534</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45924</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45579</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45929</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45644</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44974</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45755</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45580</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45928</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44839</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45928</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>46153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45553</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45938</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44924</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45145</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45944</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46155</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45945</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45944</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45944</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46077</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45684</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45320</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45887</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45946</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45946</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45947</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44963</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45950</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45635</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45643</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45247</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45946</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46155</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45114</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45959</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45959</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45961</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45961</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45961</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45005</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45961</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45832</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45961</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45961</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45114</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45961</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45960</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45961</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45964</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46160</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45964</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45685</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46161</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45737</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>45427</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45763</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45841</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45559</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45575</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>45737</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45971</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45462</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45452</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>44491</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45526</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>46162</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45979</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>45978</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45576</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45978</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45979</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>46163</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45397</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45019</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45980</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45980</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45980</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45980</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44552</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45982</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45985</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45985</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45739</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45554</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45554</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>46167</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44917</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45163</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45988</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45993</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>46169</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45163</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45993</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45616</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>44494</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45995</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45994</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45645</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>46000</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45622</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45629</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46000</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>46001</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>46002</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>44659</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>46001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>46002</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>46006</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45159</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>44944</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>46006</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46006</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>44886</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45537</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45537</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>46008</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46009</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>44944</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>46009</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46171</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46174</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>46009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>46009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44610</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45331</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45216</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46171</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45250</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45919</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45748</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>46171</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>46175</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>46031</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>46031</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45512</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46031</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45260</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45338</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46035</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45526</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45001</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45616</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45616</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46041</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>46177</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>46177</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45630</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45326</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44925</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46181</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>46049</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>46181</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45771</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>46181</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45007</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45596</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45540</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44925</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>44925</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>46059</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>45225</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>46059</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45474</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45468</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45135</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>46065</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45390</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46184</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45597</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46066</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46070</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46073</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46072</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>46073</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46073</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>46077</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46076</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46078</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>46185</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46079</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46084</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46084</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>46083</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>46085</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>45453</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46189</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45646</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>44911</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45244</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>46189</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46091</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>44910</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46091</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>44973</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45625</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>46097</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>46099</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45405</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>46099</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>46100</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>46195</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>46195</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>46101</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>46196</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>46196</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>46196</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46195</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45425</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>46198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>46198</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45554</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>46107</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46198</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46111</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>46112</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45328</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>46198</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>46113</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>46113</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>46113</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>46113</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>46120</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>46120</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44886</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46122</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>46199</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>44924</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46184</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45513</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45385</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>46128</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45509</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45537</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>46203</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44845</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45229</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45559</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>44889</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>46134</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>44818</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>46134</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>44902</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45187</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>46204</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>45596</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45420</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>46204</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44641</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45616</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45719</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>46206</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45569</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45232</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45763</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45161</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45538</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45537</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>44693</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>45754</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>45226</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45453</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>46205</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45583</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>45645</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45569</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45560</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>45596</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45596</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>46213</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45677</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>45532</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46220</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>46220</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45748</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>46219</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45832</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>46219</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>46219</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45344</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45145</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45327</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>44881</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45267</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45737</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45559</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>46230</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>46230</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>46275</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46275</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45211</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>46275</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>46275</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>46234</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45151</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45541</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45541</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45069</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46234</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45559</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46234</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45453</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>46119</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45113</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>44971</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45329</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>45684</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>46280</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>46280</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>46238</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>44916</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>46281</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>44925</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>44614</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>46282</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45513</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>44860</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46282</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46282</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45740</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>45560</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45560</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45254</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45734</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>46240</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45665</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45715</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>46282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>45740</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>44925</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>44925</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45816</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>46244</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>46241</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>46241</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45518</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>46287</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45068</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45559</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>46286</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>46185</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>46244</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>45530</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>46285</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>46285</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>46285</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>46285</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45484</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>46285</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>46245</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54582,7 +54582,7 @@
         <v>46288</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>44565</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>46246</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>44572</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>44925</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45460</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>46199</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45520</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45568</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>45105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46293</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55566,7 +55566,7 @@
         <v>46248</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55644,7 +55644,7 @@
         <v>45306</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>46248</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55800,7 +55800,7 @@
         <v>46251</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45261</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>45338</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>45635</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>46252</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45589</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45589</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>46252</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>46252</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>46252</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>46251</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>46251</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>46196</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45628</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45628</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>44839</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57023,7 +57023,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57101,7 +57101,7 @@
         <v>45453</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45453</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45754</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57330,7 +57330,7 @@
         <v>45614</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45666</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>45210</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>46198</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57637,7 +57637,7 @@
         <v>46297</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57710,7 +57710,7 @@
         <v>46297</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57783,7 +57783,7 @@
         <v>46241</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>46219</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>46254</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>46254</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46195</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46251</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58231,7 +58231,7 @@
         <v>46251</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58309,7 +58309,7 @@
         <v>45701</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45600</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58455,7 +58455,7 @@
         <v>45643</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>45646</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58606,7 +58606,7 @@
         <v>45630</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45737</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45776</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>45777</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>45777</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45776</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>44875</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59137,7 +59137,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59210,7 +59210,7 @@
         <v>45782</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45783</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59366,7 +59366,7 @@
         <v>46301</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>45825</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46300</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>46241</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45785</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45296</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>45460</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>46307</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59965,7 +59965,7 @@
         <v>45793</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>44652</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60111,7 +60111,7 @@
         <v>46262</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45796</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>46307</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60340,7 +60340,7 @@
         <v>45671</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>45320</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>45794</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>46307</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60642,7 +60642,7 @@
         <v>45567</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60715,7 +60715,7 @@
         <v>46308</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>46265</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>46308</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>46266</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>45805</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61090,7 +61090,7 @@
         <v>44868</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61163,7 +61163,7 @@
         <v>46265</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61236,7 +61236,7 @@
         <v>46265</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>45807</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45807</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>46265</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>46309</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45811</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61689,7 +61689,7 @@
         <v>46309</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>46266</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45181</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61913,7 +61913,7 @@
         <v>45810</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45330</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>46269</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62142,7 +62142,7 @@
         <v>45811</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62220,7 +62220,7 @@
         <v>45603</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         <v>46269</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>46267</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45483</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>46268</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45817</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45817</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>45819</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45820</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45825</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>45825</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>46267</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63204,7 +63204,7 @@
         <v>46267</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>46269</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63355,7 +63355,7 @@
         <v>45827</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63433,7 +63433,7 @@
         <v>45831</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>45831</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>45829</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>45831</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45832</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>45832</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63896,7 +63896,7 @@
         <v>45835</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>45835</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64052,7 +64052,7 @@
         <v>45835</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64130,7 +64130,7 @@
         <v>45834</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>45835</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>45838</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64354,7 +64354,7 @@
         <v>45841</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45847</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>45861</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>45861</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45867</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45867</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45868</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45875</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45875</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>45875</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>45882</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>45882</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>45882</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65363,7 +65363,7 @@
         <v>44463</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44635</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45673</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>45392</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65660,7 +65660,7 @@
         <v>44607</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65738,7 +65738,7 @@
         <v>44603</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65816,7 +65816,7 @@
         <v>44713</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65889,7 +65889,7 @@
         <v>45249</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44904</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66045,7 +66045,7 @@
         <v>44635</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66118,7 +66118,7 @@
         <v>45747</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66196,7 +66196,7 @@
         <v>45747</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>45747</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66352,7 +66352,7 @@
         <v>45747</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66430,7 +66430,7 @@
         <v>45747</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66508,7 +66508,7 @@
         <v>45776</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45775</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66659,7 +66659,7 @@
         <v>45916</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>46114</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>46149</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46198</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>46122</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>44788</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>45457</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45863</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45505</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45611</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45740</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>46189</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46234</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45217</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45310</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45457</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>46189</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>46241</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44690</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4978,7 +4978,7 @@
         <v>45811</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>44917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>46100</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>46226</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46245</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45842</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45617</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45666</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45155</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44924</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>46083</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>46212</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>45148</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45254</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>46301</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45793</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>45825</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>44742</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45230</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>45170</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>45944</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         <v>45436</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>46164</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>45385</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>46181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>46077</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45737</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>46191</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>45630</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>46198</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>46114</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>45159</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46246</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>46248</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45516</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44949</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>45159</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45793</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45832</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45867</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>44351</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44635</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>44943</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44845</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44872</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44652</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>44488</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44797</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>44500</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44715</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44509</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44614</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>44685</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>44797</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>44581</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44860</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>44743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>44540</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>44721</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13831,7 +13831,7 @@
         <v>44488</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>44684</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44803</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>44854</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>44915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44490</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45453</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45644</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45551</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45208</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45517</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45520</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>44851</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45463</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45775</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45212</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45455</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45238</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45510</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45159</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>44883</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45299</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44902</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>45019</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>45167</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45104</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15925,7 +15925,7 @@
         <v>44777</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>45527</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         <v>44889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45148</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44902</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>45583</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45309</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44942</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44935</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>44935</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>44935</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45533</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45616</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44971</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45729</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44910</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44916</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45721</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45518</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45159</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45069</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45240</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44882</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44962</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45148</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45740</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>44673</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44840</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45646</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45019</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45250</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45684</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>45155</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>45063</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45103</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>45104</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45251</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>45723</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>44987</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45576</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>45642</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45105</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44559</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44685</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45226</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45279</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45434</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45299</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45623</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45609</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>45513</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45463</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>45520</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45525</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45148</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45513</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45714</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45114</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45686</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>45685</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45460</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>45463</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20931,7 +20931,7 @@
         <v>45887</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>45061</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21077,7 +21077,7 @@
         <v>45162</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45219</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>44749</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44794</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>46139</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45863</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45560</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>45560</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21759,7 +21759,7 @@
         <v>45559</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45545</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45510</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21993,7 +21993,7 @@
         <v>45803</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45506</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45894</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46136</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45896</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45838</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45896</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45896</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45897</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>45901</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45706</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45884</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45842</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45789</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45514</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44644</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45539</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45898</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45674</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45616</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>46140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45511</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45565</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45316</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45905</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45175</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45909</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45387</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45537</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45915</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45915</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45915</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>45912</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45915</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>45915</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45915</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45912</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45912</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45912</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45915</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45523</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45916</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>45916</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44825</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45919</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>45918</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>45919</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45728</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45924</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26216,7 +26216,7 @@
         <v>45534</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44749</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45924</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45579</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45929</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26586,7 +26586,7 @@
         <v>45644</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44974</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45755</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45580</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>45928</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26956,7 +26956,7 @@
         <v>44839</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45928</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>46153</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45553</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45938</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44924</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45145</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27648,7 +27648,7 @@
         <v>45939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45944</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>46155</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45945</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45944</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45944</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>46077</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45684</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45320</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45887</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45946</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45946</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45947</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44963</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45950</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45635</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45643</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45247</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45952</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45946</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45952</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>46155</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45114</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45959</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45959</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45959</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45961</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45961</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45961</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45961</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45005</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45961</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45832</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45961</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45961</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45114</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45961</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45960</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45961</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45964</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46160</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45964</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>45685</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46161</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45737</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>45427</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45763</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45841</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>45559</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45575</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>45737</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>46160</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45971</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45973</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>45973</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45462</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45452</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>44491</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         <v>45526</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>46162</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45979</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>45978</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45576</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45978</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45979</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>46163</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45397</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45019</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45980</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45980</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45980</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45980</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44552</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45982</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45985</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45985</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45739</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45554</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>45554</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>46167</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>44917</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>45163</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45988</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45993</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34149,7 +34149,7 @@
         <v>46169</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45993</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45163</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45993</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45616</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>44494</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45995</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45994</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45645</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45999</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>46000</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45622</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45629</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>46000</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>46001</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>46002</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35337,7 +35337,7 @@
         <v>44659</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>46001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35483,7 +35483,7 @@
         <v>46002</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>46006</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35634,7 +35634,7 @@
         <v>45159</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
         <v>44944</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>46006</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>46006</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>44886</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45537</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45537</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>46008</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>46009</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36306,7 +36306,7 @@
         <v>44944</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>46009</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46171</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46174</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>46009</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36686,7 +36686,7 @@
         <v>46009</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>44610</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>45331</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45216</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45230</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>46171</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>45250</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>45919</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45748</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>46171</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37451,7 +37451,7 @@
         <v>46175</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>46031</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>46031</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45512</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37748,7 +37748,7 @@
         <v>46031</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37821,7 +37821,7 @@
         <v>45260</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45338</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>46035</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45526</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45001</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45616</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45616</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46041</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>46177</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>46177</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45630</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38659,7 +38659,7 @@
         <v>45326</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>44925</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>46181</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>46049</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>46181</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45771</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>46181</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45007</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45596</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39341,7 +39341,7 @@
         <v>45540</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39419,7 +39419,7 @@
         <v>44925</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>44925</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>46059</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>45225</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>46059</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>45474</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45468</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45135</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>46065</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45390</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>46184</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45597</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>46066</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46070</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46073</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>46072</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40705,7 +40705,7 @@
         <v>46073</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46073</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>46077</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         <v>46076</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46078</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>46185</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46079</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>46084</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>46084</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>46083</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>46085</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>45453</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>46189</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45646</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>44911</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41908,7 +41908,7 @@
         <v>45244</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>46189</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>46091</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42127,7 +42127,7 @@
         <v>44910</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46091</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>44973</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45625</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>46097</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>46099</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45405</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>46099</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>46100</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>46195</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>46195</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>46101</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>46196</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>46196</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>46196</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>46195</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45425</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>46198</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>46198</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45554</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>46107</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46198</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46111</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>46112</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45328</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>46198</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44236,7 +44236,7 @@
         <v>46113</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>46113</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>46113</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44465,7 +44465,7 @@
         <v>46113</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44538,7 +44538,7 @@
         <v>46120</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>46120</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44886</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>46122</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>46199</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>44924</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>46184</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45513</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45385</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45220,7 +45220,7 @@
         <v>46128</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45509</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45537</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>46203</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>44845</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>45229</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45559</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>44889</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>46134</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45902,7 +45902,7 @@
         <v>45104</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>44818</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46053,7 +46053,7 @@
         <v>46134</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46131,7 +46131,7 @@
         <v>44902</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46204,7 +46204,7 @@
         <v>45187</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>46204</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>45596</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45420</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>46204</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44641</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>45616</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45719</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>46206</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45569</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>45232</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47037,7 +47037,7 @@
         <v>45763</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>45161</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45538</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>45537</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47349,7 +47349,7 @@
         <v>44693</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>45754</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47495,7 +47495,7 @@
         <v>45226</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45453</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>46205</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>45583</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>45645</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45569</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45560</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48031,7 +48031,7 @@
         <v>45596</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>45596</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>46213</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48255,7 +48255,7 @@
         <v>45677</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>45532</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>46220</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>46220</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45748</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48635,7 +48635,7 @@
         <v>46219</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45832</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>46219</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>46219</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>46219</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>45344</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45145</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45327</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>44881</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45267</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49468,7 +49468,7 @@
         <v>45737</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>45559</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>46230</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>46230</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>46275</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46275</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45211</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>46275</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>46275</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>46234</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45151</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45541</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45541</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45069</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46234</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45559</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46234</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45453</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>46119</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45113</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>44971</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45329</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>45684</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>46280</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51295,7 +51295,7 @@
         <v>46237</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>46280</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51446,7 +51446,7 @@
         <v>46238</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51519,7 +51519,7 @@
         <v>44916</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51597,7 +51597,7 @@
         <v>46281</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>44925</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>44614</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>46282</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>45513</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>44860</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46282</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>46282</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45740</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>45560</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45560</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52420,7 +52420,7 @@
         <v>45254</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52493,7 +52493,7 @@
         <v>45734</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>46240</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>45665</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>46282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45715</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>46282</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>45740</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>44925</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>44925</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>45816</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>46244</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>46241</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>46241</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45518</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53545,7 +53545,7 @@
         <v>46287</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45068</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45559</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53769,7 +53769,7 @@
         <v>46286</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>46185</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>46244</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>45530</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>46285</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>46285</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>46285</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>46285</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45484</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>46285</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>46245</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54582,7 +54582,7 @@
         <v>46288</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>44565</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>46246</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54806,7 +54806,7 @@
         <v>44572</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>44925</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45460</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55030,7 +55030,7 @@
         <v>46199</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55103,7 +55103,7 @@
         <v>45520</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45568</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>46247</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>45105</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55488,7 +55488,7 @@
         <v>46293</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55566,7 +55566,7 @@
         <v>46248</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55644,7 +55644,7 @@
         <v>45306</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55722,7 +55722,7 @@
         <v>46248</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55800,7 +55800,7 @@
         <v>46251</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55878,7 +55878,7 @@
         <v>45261</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>45338</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>45635</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>46252</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>45589</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45589</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>46252</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>46252</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>46252</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56560,7 +56560,7 @@
         <v>46251</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>46251</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>46196</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>45628</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56867,7 +56867,7 @@
         <v>45628</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>44839</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57023,7 +57023,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57101,7 +57101,7 @@
         <v>45453</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45453</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57257,7 +57257,7 @@
         <v>45754</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57330,7 +57330,7 @@
         <v>45614</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45666</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>45210</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>46198</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57637,7 +57637,7 @@
         <v>46297</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57710,7 +57710,7 @@
         <v>46297</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57783,7 +57783,7 @@
         <v>46241</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>46219</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57934,7 +57934,7 @@
         <v>46254</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>46254</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46195</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46251</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58231,7 +58231,7 @@
         <v>46251</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58309,7 +58309,7 @@
         <v>45701</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45600</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58455,7 +58455,7 @@
         <v>45643</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>45646</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58606,7 +58606,7 @@
         <v>45630</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45737</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45776</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>45777</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>45777</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45776</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>44875</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59137,7 +59137,7 @@
         <v>46300</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59210,7 +59210,7 @@
         <v>45782</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45783</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59366,7 +59366,7 @@
         <v>46301</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>45825</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46300</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         <v>46241</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45785</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59736,7 +59736,7 @@
         <v>45296</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59809,7 +59809,7 @@
         <v>45460</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>46307</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59965,7 +59965,7 @@
         <v>45793</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>44652</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60111,7 +60111,7 @@
         <v>46262</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45796</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>46307</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60340,7 +60340,7 @@
         <v>45671</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>45320</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>45794</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60564,7 +60564,7 @@
         <v>46307</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60642,7 +60642,7 @@
         <v>45567</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60715,7 +60715,7 @@
         <v>46308</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>46265</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>46308</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>46266</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>45805</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61090,7 +61090,7 @@
         <v>44868</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61163,7 +61163,7 @@
         <v>46265</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61236,7 +61236,7 @@
         <v>46265</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>45807</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45807</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>46265</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>46309</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61611,7 +61611,7 @@
         <v>45811</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61689,7 +61689,7 @@
         <v>46309</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>46266</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45181</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61913,7 +61913,7 @@
         <v>45810</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45330</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>46269</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62142,7 +62142,7 @@
         <v>45811</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62220,7 +62220,7 @@
         <v>45603</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         <v>46269</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>46267</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45483</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62527,7 +62527,7 @@
         <v>46268</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45817</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45817</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62829,7 +62829,7 @@
         <v>45819</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>45820</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45825</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63053,7 +63053,7 @@
         <v>45825</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63126,7 +63126,7 @@
         <v>46267</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63204,7 +63204,7 @@
         <v>46267</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63277,7 +63277,7 @@
         <v>46269</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63355,7 +63355,7 @@
         <v>45827</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63433,7 +63433,7 @@
         <v>45831</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>45831</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>45829</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>45831</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45832</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>45832</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63896,7 +63896,7 @@
         <v>45835</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63974,7 +63974,7 @@
         <v>45835</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64052,7 +64052,7 @@
         <v>45835</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64130,7 +64130,7 @@
         <v>45834</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>45835</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64281,7 +64281,7 @@
         <v>45838</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64354,7 +64354,7 @@
         <v>45841</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45847</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64510,7 +64510,7 @@
         <v>45861</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>45861</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45867</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45867</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45868</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45875</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45875</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>45875</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>45882</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>45882</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65285,7 +65285,7 @@
         <v>45882</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65363,7 +65363,7 @@
         <v>44463</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44635</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>45673</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>45392</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65660,7 +65660,7 @@
         <v>44607</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65738,7 +65738,7 @@
         <v>44603</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65816,7 +65816,7 @@
         <v>44713</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65889,7 +65889,7 @@
         <v>45249</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44904</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66045,7 +66045,7 @@
         <v>44635</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66118,7 +66118,7 @@
         <v>45747</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66196,7 +66196,7 @@
         <v>45747</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>45747</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66352,7 +66352,7 @@
         <v>45747</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66430,7 +66430,7 @@
         <v>45747</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66508,7 +66508,7 @@
         <v>45776</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45775</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66659,7 +66659,7 @@
         <v>45916</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>46114</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66805,7 +66805,7 @@
         <v>46149</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46198</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45457</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45863</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46122</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44788</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>46189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45611</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45740</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45310</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45217</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46189</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46241</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45811</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45457</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46226</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46245</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45813</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>46100</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46212</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45254</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>46083</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>46301</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45155</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45666</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45617</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45148</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45933</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45630</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>46191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>46203</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45516</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44949</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>46280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45793</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>46246</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46248</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>46077</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45737</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45832</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45159</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>46114</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45867</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45385</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45230</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45159</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45170</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>44742</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45436</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>44351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44635</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44693</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44652</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44797</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44500</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44715</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44614</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44509</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44581</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>44797</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44860</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>44743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44540</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44721</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44684</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44854</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44818</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45338</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44794</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45553</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45510</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44839</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45512</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44825</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45596</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45622</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45463</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45896</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45896</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45898</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45723</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45897</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45208</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45754</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44659</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45905</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45841</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45559</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45909</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45911</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46161</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45912</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45912</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45912</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45832</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45912</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45911</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45915</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45916</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45915</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45915</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45915</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45915</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45915</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45915</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45916</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45387</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45523</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>46162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45151</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45210</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45919</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45919</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45565</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45924</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44886</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46169</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45928</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>46171</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45928</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>46171</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>46171</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>46174</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45936</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45057</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46175</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45939</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45684</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45944</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45944</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45148</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46177</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45684</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45944</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46177</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45453</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45225</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45455</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45299</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45420</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45946</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45646</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45453</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45453</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45775</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45946</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>46181</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45114</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45576</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45453</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45532</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46181</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44902</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45559</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45520</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44860</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45952</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45952</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45460</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44559</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45946</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45677</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45105</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45625</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>46185</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45628</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45616</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45145</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>46184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>44925</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45959</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>46185</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45959</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45961</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45961</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45961</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>46189</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45964</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45961</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45961</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45961</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45964</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45961</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45961</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45961</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46188</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44911</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45261</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44845</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45328</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46195</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>46195</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45215</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46195</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>46196</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45560</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45973</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>46196</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45686</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45973</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45069</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45666</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>46196</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>46196</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45978</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45978</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45763</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>46198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>46198</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>46199</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45979</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>46198</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45748</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45980</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45979</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44987</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45980</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45511</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>46203</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45979</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45397</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45729</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45980</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>46184</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45159</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>46205</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45453</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45982</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>46204</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45985</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45985</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>46204</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46206</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45988</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45530</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45541</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45541</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45685</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45644</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>46213</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44962</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45306</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45993</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45993</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45993</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45630</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44944</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45995</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45701</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>46000</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46000</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46219</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44572</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>46219</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>46219</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>46219</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45999</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46220</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45509</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>46220</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45776</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45776</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45832</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>46001</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45777</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>46001</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>46002</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>46002</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45777</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44875</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44889</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45782</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>46006</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>46006</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>46008</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46230</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45559</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>46230</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45783</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>46280</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>46009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>46009</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45247</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>46009</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46009</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>46280</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>46237</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46234</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>46119</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45785</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46234</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>46234</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45919</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>46238</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>46281</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>46282</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46282</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45460</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>46282</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>46282</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45453</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46285</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46285</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>46031</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>46031</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45296</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>46285</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>46185</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>46286</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45463</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44652</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>46241</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45671</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>46035</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46285</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>46285</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45793</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45320</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>46241</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45794</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>46041</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>46287</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>46288</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45796</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>46244</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>45816</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>46245</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>46049</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45567</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45545</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>46199</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45805</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44868</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>46246</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>46247</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>44882</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45520</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45807</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45807</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45330</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45810</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45811</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>46059</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45468</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46248</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45474</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46293</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>46248</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>46059</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45603</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46293</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>45811</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45817</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>46065</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46066</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46070</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45817</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45483</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46251</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46072</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45511</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45819</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45820</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>46073</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44881</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44883</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>46073</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46252</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>46076</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46073</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46077</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46079</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46251</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45825</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>46078</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46252</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>46252</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45825</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45827</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>46252</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46083</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46251</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45831</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45832</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45832</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45829</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45831</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>46084</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46085</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45831</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45834</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>46084</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46300</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>46241</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>46254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>46297</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46254</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>46195</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45835</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45835</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>46091</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>46091</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45835</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45838</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45835</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>46300</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>46219</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46241</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46097</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>45506</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>46198</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>44839</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45537</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46099</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>46196</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45841</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44902</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46099</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46251</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44735,7 +44735,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>46297</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>46101</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>46100</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>46198</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>46301</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>45847</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45825</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46107</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>46107</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>46111</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46112</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>46113</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45861</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>46113</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45861</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>46113</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45868</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45867</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45867</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46120</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>46120</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>46122</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45537</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45875</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45875</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45875</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>46262</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>46265</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46128</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46307</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>46265</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>46307</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>45329</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45882</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45882</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45882</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45537</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45538</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>46134</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>46308</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46134</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45425</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46307</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>45737</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>46308</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>46265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>46136</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46266</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45513</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>46266</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>44924</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>46309</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>46309</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>45842</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>46267</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45674</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45616</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45616</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45616</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>44942</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45525</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46267</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>46269</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44552</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>46314</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>46314</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>46314</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45162</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46314</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>46269</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45007</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>46314</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45789</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45187</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>46314</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50747,7 +50747,7 @@
         <v>45240</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>46269</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45838</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>46314</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>46314</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>46269</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>46314</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>46268</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>46314</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46314</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45513</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46139</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>46316</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45232</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>46140</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45884</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45863</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>44614</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45514</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45161</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45517</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45721</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45554</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46318</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45061</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52662,7 +52662,7 @@
         <v>46318</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>46318</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44971</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45453</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>45511</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>46275</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>46275</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45539</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45385</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45212</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>45616</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53500,7 +53500,7 @@
         <v>45583</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>44916</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46275</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>44610</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>46275</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45569</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53958,7 +53958,7 @@
         <v>45526</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54036,7 +54036,7 @@
         <v>44641</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45684</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
         <v>46153</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45226</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45630</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>44944</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45635</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>46155</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46155</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45887</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46077</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45260</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46160</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46160</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>45019</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45299</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>44924</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>45219</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45643</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44925</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44971</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45019</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>45163</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45155</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45068</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45005</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45114</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>45114</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45103</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>45104</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>44565</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45714</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>45646</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45685</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56588,7 +56588,7 @@
         <v>45665</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>45646</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45706</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56807,7 +56807,7 @@
         <v>45513</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45737</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56958,7 +56958,7 @@
         <v>45739</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45554</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>44749</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57177,7 +57177,7 @@
         <v>44886</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57250,7 +57250,7 @@
         <v>45526</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45737</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45250</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>45043</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57547,7 +57547,7 @@
         <v>45755</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45534</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45069</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57771,7 +57771,7 @@
         <v>44851</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45771</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57922,7 +57922,7 @@
         <v>44644</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>44925</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58068,7 +58068,7 @@
         <v>45597</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>45740</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>44910</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58287,7 +58287,7 @@
         <v>45560</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>45596</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45460</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45559</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45559</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45576</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>45113</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45320</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45644</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>45344</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45551</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59120,7 +59120,7 @@
         <v>45105</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59193,7 +59193,7 @@
         <v>45580</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59266,7 +59266,7 @@
         <v>45537</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45537</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59422,7 +59422,7 @@
         <v>44935</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>44935</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59578,7 +59578,7 @@
         <v>44935</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>45602</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>44494</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>45510</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         <v>44973</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>45575</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60026,7 +60026,7 @@
         <v>45616</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45527</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45754</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60250,7 +60250,7 @@
         <v>44916</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45019</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60401,7 +60401,7 @@
         <v>45569</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45148</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60552,7 +60552,7 @@
         <v>45145</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>45114</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         <v>45518</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>45518</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60849,7 +60849,7 @@
         <v>45533</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45635</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61000,7 +61000,7 @@
         <v>45155</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45159</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>45554</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>45513</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45614</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>45568</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61453,7 +61453,7 @@
         <v>45559</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61531,7 +61531,7 @@
         <v>45596</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>45628</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45452</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45104</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45609</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45579</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>45737</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62062,7 +62062,7 @@
         <v>45216</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>45645</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>45589</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>45427</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45063</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>45629</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45715</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45623</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45167</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>45728</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>44673</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45434</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62958,7 +62958,7 @@
         <v>45159</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>45645</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45583</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45642</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45763</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63338,7 +63338,7 @@
         <v>45740</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63411,7 +63411,7 @@
         <v>44777</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63489,7 +63489,7 @@
         <v>44693</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63562,7 +63562,7 @@
         <v>45226</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63640,7 +63640,7 @@
         <v>45463</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63718,7 +63718,7 @@
         <v>45211</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63791,7 +63791,7 @@
         <v>44910</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63869,7 +63869,7 @@
         <v>45643</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63947,7 +63947,7 @@
         <v>45135</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>45316</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64098,7 +64098,7 @@
         <v>45238</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64171,7 +64171,7 @@
         <v>45230</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>45327</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>44974</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64395,7 +64395,7 @@
         <v>45309</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>45163</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>45254</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>45250</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>44749</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45462</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64848,7 +64848,7 @@
         <v>44925</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64921,7 +64921,7 @@
         <v>45229</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64994,7 +64994,7 @@
         <v>45484</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65067,7 +65067,7 @@
         <v>45748</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65145,7 +65145,7 @@
         <v>44685</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65218,7 +65218,7 @@
         <v>45163</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65291,7 +65291,7 @@
         <v>45148</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>45740</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>45589</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>45326</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65593,7 +65593,7 @@
         <v>45405</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45520</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65744,7 +65744,7 @@
         <v>45560</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65822,7 +65822,7 @@
         <v>45560</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65900,7 +65900,7 @@
         <v>44915</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>44925</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66051,7 +66051,7 @@
         <v>44925</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66124,7 +66124,7 @@
         <v>45331</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66202,7 +66202,7 @@
         <v>44917</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66275,7 +66275,7 @@
         <v>45560</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>44463</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66426,7 +66426,7 @@
         <v>44635</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>44607</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         <v>44603</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66655,7 +66655,7 @@
         <v>44713</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66728,7 +66728,7 @@
         <v>44635</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66801,7 +66801,7 @@
         <v>45673</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66879,7 +66879,7 @@
         <v>45392</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>45249</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67030,7 +67030,7 @@
         <v>44904</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67108,7 +67108,7 @@
         <v>45747</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67186,7 +67186,7 @@
         <v>45747</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67264,7 +67264,7 @@
         <v>45747</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         <v>45747</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67420,7 +67420,7 @@
         <v>45747</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67498,7 +67498,7 @@
         <v>45776</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67576,7 +67576,7 @@
         <v>45775</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>45916</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>46114</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67795,7 +67795,7 @@
         <v>46149</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>

--- a/Översikt VINDELN.xlsx
+++ b/Översikt VINDELN.xlsx
@@ -601,7 +601,7 @@
         <v>46134</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>45863</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46029</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>45939</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>44493</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>46198</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45457</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>45863</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>46122</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>44788</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>46135</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>44515</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>44991</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>44532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>45511</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>46266</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44559</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45701</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>46176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>45505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>46189</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>46234</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>45611</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45740</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46070</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45310</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45217</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>46189</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46241</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>45811</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45457</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>45250</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>44512</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>46226</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46245</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>45813</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45842</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>46100</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>46314</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>46212</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45793</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>45254</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45825</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>46083</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>46301</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>45155</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45666</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45617</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44924</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45148</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46164</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45933</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45944</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>45630</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>46191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46198</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>46203</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45516</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44949</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>46280</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45793</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>46246</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>46070</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>46248</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>46077</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45737</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45832</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45159</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>46114</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>45867</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45875</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>45385</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45230</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45159</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45170</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>44742</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45436</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>44351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>44635</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44845</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44693</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44652</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44876</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44559</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44714</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44797</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44875</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44500</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44715</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44536</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>44872</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44614</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44509</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44537</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>44817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44679</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44581</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>44685</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>44797</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>44536</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>44860</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44872</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>44743</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>44540</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>44511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44820</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>44600</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>44713</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>44721</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>44684</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>44803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44854</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44818</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45244</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45338</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>44794</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45728</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45553</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45510</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44839</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45512</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>44825</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45596</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45596</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45622</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45463</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45896</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45251</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45896</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45898</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45723</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45897</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>45208</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44889</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45754</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>45104</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44659</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45338</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44902</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>45905</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>45841</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>45559</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45909</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45174</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45911</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>46161</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45912</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45912</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45912</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45832</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45912</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45911</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45915</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45916</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45915</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45915</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>46163</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45915</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45915</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45915</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45915</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45915</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45915</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45915</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45916</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45387</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45523</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>46162</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45918</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45151</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45210</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45919</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45919</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45565</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>45175</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45924</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44886</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46169</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45928</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45929</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>46171</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45928</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>46171</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>46171</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>46174</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45936</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45938</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45057</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45390</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>46175</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>45939</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45684</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45944</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45944</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45148</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>46177</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45684</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45944</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>46177</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44840</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>45453</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>45225</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>45455</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45299</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45420</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45946</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45646</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45453</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45453</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45775</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45946</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>46181</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45114</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45576</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45453</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45532</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45947</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46181</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44902</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45559</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>45520</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>44860</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45952</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23640,7 +23640,7 @@
         <v>45952</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23713,7 +23713,7 @@
         <v>45460</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44559</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23859,7 +23859,7 @@
         <v>45946</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45677</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>45105</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45625</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>46185</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45628</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45616</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45145</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>46184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24614,7 +24614,7 @@
         <v>44925</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45959</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24765,7 +24765,7 @@
         <v>45959</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24838,7 +24838,7 @@
         <v>46185</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45959</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45960</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45961</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45961</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45961</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>46189</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45964</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>45961</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45961</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45961</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45964</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45961</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45961</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45961</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>46189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46188</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44911</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45261</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44845</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45328</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46195</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>45971</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>46195</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45215</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>46195</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>46196</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45560</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45973</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>46196</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>45686</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27151,7 +27151,7 @@
         <v>45973</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45069</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45666</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>46196</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>46196</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>46198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45978</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45978</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45763</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>46198</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>46198</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>44963</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>46199</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45979</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28213,7 +28213,7 @@
         <v>46198</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45748</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>45980</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45979</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>44987</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45980</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28749,7 +28749,7 @@
         <v>45511</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28822,7 +28822,7 @@
         <v>46203</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45979</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45397</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45729</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45980</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>46184</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45159</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>46205</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45453</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>45982</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>46204</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>45985</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45985</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>46204</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>46206</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>45988</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45530</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45541</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>45541</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45685</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>45644</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30483,7 +30483,7 @@
         <v>46213</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>44962</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45306</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>45993</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>45993</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45993</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31004,7 +31004,7 @@
         <v>45630</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44944</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45995</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>45701</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>46000</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31384,7 +31384,7 @@
         <v>46000</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>46219</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         <v>44572</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>46219</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>46219</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>46219</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>45999</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31915,7 +31915,7 @@
         <v>46220</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45509</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>46220</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45776</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45776</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45832</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>46001</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>45777</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>46001</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32592,7 +32592,7 @@
         <v>46002</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>46002</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45777</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>44875</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44889</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45782</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>46006</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>46006</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>46006</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>46008</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>46230</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45559</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>46230</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33581,7 +33581,7 @@
         <v>45783</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>46280</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>46009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>46009</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45247</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>46009</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46009</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>46280</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34170,7 +34170,7 @@
         <v>46237</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>46234</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>46119</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45785</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>46234</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>46234</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45919</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>46238</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>46281</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>46282</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46282</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45460</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>46282</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>46282</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>45453</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>46285</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>46285</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>46031</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>46031</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45296</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>46031</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>46285</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>46185</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>46286</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45267</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>45463</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44652</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>46241</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45671</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>46035</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>46285</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>46285</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>45793</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>45320</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>46241</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45794</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>46041</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>46287</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>46288</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45796</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>46244</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>46244</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37472,7 +37472,7 @@
         <v>45816</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>46245</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>46049</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45567</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37774,7 +37774,7 @@
         <v>45545</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>46199</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45805</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>44868</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38076,7 +38076,7 @@
         <v>46246</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38154,7 +38154,7 @@
         <v>46247</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>44882</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38305,7 +38305,7 @@
         <v>45520</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45807</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45279</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38539,7 +38539,7 @@
         <v>45181</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45807</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45330</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>45810</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45811</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38919,7 +38919,7 @@
         <v>46059</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45468</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>46248</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45474</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46293</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39309,7 +39309,7 @@
         <v>46248</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>46059</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45603</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39538,7 +39538,7 @@
         <v>46293</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>45811</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39694,7 +39694,7 @@
         <v>45817</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39767,7 +39767,7 @@
         <v>46065</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39845,7 +39845,7 @@
         <v>46066</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39918,7 +39918,7 @@
         <v>46070</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>45817</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45483</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>46251</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>46072</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45511</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45819</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45820</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40532,7 +40532,7 @@
         <v>46073</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40605,7 +40605,7 @@
         <v>44881</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44883</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>46073</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46252</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>46076</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>46073</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>46077</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>46079</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>46251</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45825</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>46078</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41423,7 +41423,7 @@
         <v>46252</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>46252</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45825</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>45827</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>46252</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>46083</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46251</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45831</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45832</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45832</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45829</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45831</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>46084</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42412,7 +42412,7 @@
         <v>46085</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>45831</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45834</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>46084</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>46300</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>46241</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>46254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>46297</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>46254</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>46195</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45835</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45835</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>46091</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>46091</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>45835</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45838</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45835</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>46300</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>46219</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46241</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43907,7 +43907,7 @@
         <v>46097</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         <v>45506</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>46198</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>44839</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45537</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>46099</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>46196</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45841</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44902</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>46099</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46251</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44735,7 +44735,7 @@
         <v>46251</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>46297</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>46101</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>46100</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>46198</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45115,7 +45115,7 @@
         <v>46301</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45188,7 +45188,7 @@
         <v>45847</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45825</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>46107</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45417,7 +45417,7 @@
         <v>46107</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>46111</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>46112</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45641,7 +45641,7 @@
         <v>46113</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45861</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>46113</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45861</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>46113</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>45868</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>45867</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45867</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46120</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>46120</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>46122</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45537</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         <v>45875</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45875</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45875</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>46262</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>46265</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46128</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47093,7 +47093,7 @@
         <v>46307</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>46265</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>46307</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>45329</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45882</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>45882</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>45882</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47629,7 +47629,7 @@
         <v>45537</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45538</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>46134</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>46308</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46134</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45425</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48087,7 +48087,7 @@
         <v>46307</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>45737</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48238,7 +48238,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>46308</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>46265</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>46136</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46266</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45513</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>46266</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>44924</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>46309</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>46309</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>45842</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>46267</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>45674</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45616</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45616</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45616</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>44942</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49597,7 +49597,7 @@
         <v>45525</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>46267</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>46269</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>44552</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>46314</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>46314</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50060,7 +50060,7 @@
         <v>46314</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50138,7 +50138,7 @@
         <v>45162</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>46314</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>46269</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45007</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>46314</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50523,7 +50523,7 @@
         <v>45789</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45187</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50669,7 +50669,7 @@
         <v>46314</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50747,7 +50747,7 @@
         <v>45240</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>46269</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45838</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>46314</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>46314</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>46269</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>46314</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>46268</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51356,7 +51356,7 @@
         <v>46314</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>46314</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45513</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46139</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>46316</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51746,7 +51746,7 @@
         <v>45232</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>46140</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51902,7 +51902,7 @@
         <v>45884</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>45863</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52058,7 +52058,7 @@
         <v>44614</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45514</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45161</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45517</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45721</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45554</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52511,7 +52511,7 @@
         <v>46318</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52589,7 +52589,7 @@
         <v>45061</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52662,7 +52662,7 @@
         <v>46318</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52740,7 +52740,7 @@
         <v>46318</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>44971</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45453</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52969,7 +52969,7 @@
         <v>45511</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53042,7 +53042,7 @@
         <v>46275</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>46275</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45539</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45385</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45212</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>45616</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53500,7 +53500,7 @@
         <v>45583</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53573,7 +53573,7 @@
         <v>44916</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>46275</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53729,7 +53729,7 @@
         <v>44610</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>46275</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53880,7 +53880,7 @@
         <v>45569</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53958,7 +53958,7 @@
         <v>45526</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -54036,7 +54036,7 @@
         <v>44641</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54109,7 +54109,7 @@
         <v>45684</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54182,7 +54182,7 @@
         <v>46153</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45226</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45630</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54416,7 +54416,7 @@
         <v>44944</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54494,7 +54494,7 @@
         <v>45635</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54572,7 +54572,7 @@
         <v>46155</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46155</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45887</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46077</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45260</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46160</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46160</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>45019</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45299</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>44924</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>45219</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45643</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44925</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44971</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45019</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>45163</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45155</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>45068</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55921,7 +55921,7 @@
         <v>45005</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55994,7 +55994,7 @@
         <v>45114</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>45114</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56140,7 +56140,7 @@
         <v>45103</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56213,7 +56213,7 @@
         <v>45104</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>44565</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45714</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>45646</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45685</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56588,7 +56588,7 @@
         <v>45665</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>45646</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         <v>45706</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56807,7 +56807,7 @@
         <v>45513</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56885,7 +56885,7 @@
         <v>45737</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56958,7 +56958,7 @@
         <v>45739</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57031,7 +57031,7 @@
         <v>45554</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57104,7 +57104,7 @@
         <v>44749</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57177,7 +57177,7 @@
         <v>44886</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57250,7 +57250,7 @@
         <v>45526</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45737</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>45250</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>45043</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57547,7 +57547,7 @@
         <v>45755</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57625,7 +57625,7 @@
         <v>45534</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45069</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57771,7 +57771,7 @@
         <v>44851</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45771</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57922,7 +57922,7 @@
         <v>44644</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57995,7 +57995,7 @@
         <v>44925</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58068,7 +58068,7 @@
         <v>45597</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>45740</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>44910</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58287,7 +58287,7 @@
         <v>45560</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>45596</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45460</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45559</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45559</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45576</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>45113</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45320</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45644</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>45344</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45551</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59120,7 +59120,7 @@
         <v>45105</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59193,7 +59193,7 @@
         <v>45580</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59266,7 +59266,7 @@
         <v>45537</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45537</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59422,7 +59422,7 @@
         <v>44935</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59500,7 +59500,7 @@
         <v>44935</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59578,7 +59578,7 @@
         <v>44935</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>45602</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>44494</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>45510</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         <v>44973</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>45575</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60026,7 +60026,7 @@
         <v>45616</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45527</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45754</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60250,7 +60250,7 @@
         <v>44916</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45019</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60401,7 +60401,7 @@
         <v>45569</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60479,7 +60479,7 @@
         <v>45148</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60552,7 +60552,7 @@
         <v>45145</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>45114</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60703,7 +60703,7 @@
         <v>45518</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>45518</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60849,7 +60849,7 @@
         <v>45533</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45635</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -61000,7 +61000,7 @@
         <v>45155</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45159</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61151,7 +61151,7 @@
         <v>45554</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>45513</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61302,7 +61302,7 @@
         <v>45614</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61380,7 +61380,7 @@
         <v>45568</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61453,7 +61453,7 @@
         <v>45559</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61531,7 +61531,7 @@
         <v>45596</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61609,7 +61609,7 @@
         <v>45628</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45452</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45104</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45609</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45579</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>45737</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62062,7 +62062,7 @@
         <v>45216</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>45645</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>45589</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>45427</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45063</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>45629</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45715</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45623</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45167</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62734,7 +62734,7 @@
         <v>45728</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>44673</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62880,7 +62880,7 @@
         <v>45434</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62958,7 +62958,7 @@
         <v>45159</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>45645</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45583</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>45642</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45763</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63338,7 +63338,7 @@
         <v>45740</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63411,7 +63411,7 @@
         <v>44777</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63489,7 +63489,7 @@
         <v>44693</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63562,7 +63562,7 @@
         <v>45226</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63640,7 +63640,7 @@
         <v>45463</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63718,7 +63718,7 @@
         <v>45211</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63791,7 +63791,7 @@
         <v>44910</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63869,7 +63869,7 @@
         <v>45643</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63947,7 +63947,7 @@
         <v>45135</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>45316</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64098,7 +64098,7 @@
         <v>45238</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64171,7 +64171,7 @@
         <v>45230</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64249,7 +64249,7 @@
         <v>45327</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>44974</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64395,7 +64395,7 @@
         <v>45309</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64473,7 +64473,7 @@
         <v>45163</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>45254</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64624,7 +64624,7 @@
         <v>45250</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>44749</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45462</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64848,7 +64848,7 @@
         <v>44925</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64921,7 +64921,7 @@
         <v>45229</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64994,7 +64994,7 @@
         <v>45484</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65067,7 +65067,7 @@
         <v>45748</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65145,7 +65145,7 @@
         <v>44685</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65218,7 +65218,7 @@
         <v>45163</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65291,7 +65291,7 @@
         <v>45148</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>45740</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65437,7 +65437,7 @@
         <v>45589</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65515,7 +65515,7 @@
         <v>45326</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65593,7 +65593,7 @@
         <v>45405</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65666,7 +65666,7 @@
         <v>45520</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65744,7 +65744,7 @@
         <v>45560</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65822,7 +65822,7 @@
         <v>45560</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65900,7 +65900,7 @@
         <v>44915</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>44925</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -66051,7 +66051,7 @@
         <v>44925</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66124,7 +66124,7 @@
         <v>45331</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66202,7 +66202,7 @@
         <v>44917</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66275,7 +66275,7 @@
         <v>45560</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>44463</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66426,7 +66426,7 @@
         <v>44635</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>44607</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         <v>44603</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66655,7 +66655,7 @@
         <v>44713</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66728,7 +66728,7 @@
         <v>44635</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66801,7 +66801,7 @@
         <v>45673</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66879,7 +66879,7 @@
         <v>45392</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>45249</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -67030,7 +67030,7 @@
         <v>44904</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67108,7 +67108,7 @@
         <v>45747</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67186,7 +67186,7 @@
         <v>45747</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67264,7 +67264,7 @@
         <v>45747</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         <v>45747</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67420,7 +67420,7 @@
         <v>45747</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67498,7 +67498,7 @@
         <v>45776</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67576,7 +67576,7 @@
         <v>45775</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>45916</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -67722,7 +67722,7 @@
         <v>46114</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -67795,7 +67795,7 @@
         <v>46149</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
